--- a/cash/exportcash/BcK Uscite cassa.xlsx
+++ b/cash/exportcash/BcK Uscite cassa.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="335">
   <si>
     <t>_PK_Uscita_cassa</t>
   </si>
@@ -212,6 +212,9 @@
     <t xml:space="preserve">salaire de fin Octobre </t>
   </si>
   <si>
+    <t>2C5A3755-4690-364C-8114-BD1D63BB0FC5</t>
+  </si>
+  <si>
     <t>2DBBC101-4038-FC45-84AB-F04CBE96F8D8</t>
   </si>
   <si>
@@ -389,6 +392,9 @@
     <t>54574D76-A418-0D49-B137-41FA531C8AF2</t>
   </si>
   <si>
+    <t>551E8C59-513E-9745-92F5-917ADEC8E457</t>
+  </si>
+  <si>
     <t>557FE422-C351-2C4E-BACA-1D4A178F3CE1</t>
   </si>
   <si>
@@ -710,6 +716,9 @@
     <t>9DDAF32D-03B9-DE4E-BE46-E04C0AA44358</t>
   </si>
   <si>
+    <t>A4BC0BA3-688B-3A40-92E6-EF024905AADA</t>
+  </si>
+  <si>
     <t>A5021846-DCCC-FF45-B093-079FF9F7D258</t>
   </si>
   <si>
@@ -761,6 +770,12 @@
     <t>scolarité de kinda inoussa</t>
   </si>
   <si>
+    <t>B1121877-6F94-6743-9D23-34B153C653CD</t>
+  </si>
+  <si>
+    <t>connexion internet</t>
+  </si>
+  <si>
     <t>B1DAFDC1-4E23-7B4A-B462-E85EB9062434</t>
   </si>
   <si>
@@ -839,9 +854,6 @@
     <t>C847250C-04E9-2440-98CF-8829D03FA11B</t>
   </si>
   <si>
-    <t>connexion internet</t>
-  </si>
-  <si>
     <t>C8A49377-C73A-0144-9A75-2FAF324A49AF</t>
   </si>
   <si>
@@ -879,6 +891,12 @@
   </si>
   <si>
     <t>reparation de foyer</t>
+  </si>
+  <si>
+    <t>CFE3F8E2-1E14-1F40-865A-C56CA2D68F0F</t>
+  </si>
+  <si>
+    <t>réparation de moto</t>
   </si>
   <si>
     <t>D010E58B-2438-084D-AFBC-A5CE67354201</t>
@@ -2061,25 +2079,25 @@
         <v>67</v>
       </c>
       <c r="B34" s="7">
-        <v>45567.74461805566000528359354</v>
+        <v>45715.334756944549232476473492</v>
       </c>
       <c r="C34" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D34" s="9">
-        <v>45567.756585648252597903618076</v>
+        <v>45715.36655092603071403083268</v>
       </c>
       <c r="E34" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F34" s="11">
-        <v>45552</v>
+        <v>45714</v>
       </c>
       <c r="G34" s="12">
-        <v>21000</v>
+        <v>1000</v>
       </c>
       <c r="H34" t="s" s="13">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="I34" t="s" s="14">
         <v>12</v>
@@ -2087,28 +2105,28 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="6">
+        <v>68</v>
+      </c>
+      <c r="B35" s="7">
+        <v>45567.74461805566000528359354</v>
+      </c>
+      <c r="C35" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D35" s="9">
+        <v>45567.756585648252597903618076</v>
+      </c>
+      <c r="E35" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F35" s="11">
+        <v>45552</v>
+      </c>
+      <c r="G35" s="12">
+        <v>21000</v>
+      </c>
+      <c r="H35" t="s" s="13">
         <v>69</v>
-      </c>
-      <c r="B35" s="7">
-        <v>45567.733645833437783036220948</v>
-      </c>
-      <c r="C35" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D35" s="9">
-        <v>45567.733900463067412666434236</v>
-      </c>
-      <c r="E35" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F35" s="11">
-        <v>45567</v>
-      </c>
-      <c r="G35" s="12">
-        <v>10000</v>
-      </c>
-      <c r="H35" t="s" s="13">
-        <v>70</v>
       </c>
       <c r="I35" t="s" s="14">
         <v>12</v>
@@ -2116,28 +2134,28 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="6">
+        <v>70</v>
+      </c>
+      <c r="B36" s="7">
+        <v>45567.733645833437783036220948</v>
+      </c>
+      <c r="C36" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D36" s="9">
+        <v>45567.733900463067412666434236</v>
+      </c>
+      <c r="E36" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F36" s="11">
+        <v>45567</v>
+      </c>
+      <c r="G36" s="12">
+        <v>10000</v>
+      </c>
+      <c r="H36" t="s" s="13">
         <v>71</v>
-      </c>
-      <c r="B36" s="7">
-        <v>45632.69490740751200601356336</v>
-      </c>
-      <c r="C36" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D36" s="9">
-        <v>45632.695185185289783791977856</v>
-      </c>
-      <c r="E36" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F36" s="11">
-        <v>45632</v>
-      </c>
-      <c r="G36" s="12">
-        <v>1000</v>
-      </c>
-      <c r="H36" t="s" s="13">
-        <v>25</v>
       </c>
       <c r="I36" t="s" s="14">
         <v>12</v>
@@ -2148,25 +2166,25 @@
         <v>72</v>
       </c>
       <c r="B37" s="7">
-        <v>45678.140185185289887960352448</v>
+        <v>45632.69490740751200601356336</v>
       </c>
       <c r="C37" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D37" s="9">
-        <v>45678.142314814919517594863584</v>
+        <v>45632.695185185289783791977856</v>
       </c>
       <c r="E37" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F37" s="11">
-        <v>45678</v>
+        <v>45632</v>
       </c>
       <c r="G37" s="12">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="H37" t="s" s="13">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="I37" t="s" s="14">
         <v>12</v>
@@ -2174,28 +2192,28 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="6">
+        <v>73</v>
+      </c>
+      <c r="B38" s="7">
+        <v>45678.140185185289887960352448</v>
+      </c>
+      <c r="C38" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D38" s="9">
+        <v>45678.142314814919517594863584</v>
+      </c>
+      <c r="E38" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F38" s="11">
+        <v>45678</v>
+      </c>
+      <c r="G38" s="12">
+        <v>5000</v>
+      </c>
+      <c r="H38" t="s" s="13">
         <v>74</v>
-      </c>
-      <c r="B38" s="7">
-        <v>45593.675324074178583240102992</v>
-      </c>
-      <c r="C38" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D38" s="9">
-        <v>45593.677928240845249912738892</v>
-      </c>
-      <c r="E38" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F38" s="11">
-        <v>45593</v>
-      </c>
-      <c r="G38" s="12">
-        <v>553000</v>
-      </c>
-      <c r="H38" t="s" s="13">
-        <v>75</v>
       </c>
       <c r="I38" t="s" s="14">
         <v>12</v>
@@ -2203,28 +2221,28 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="6">
+        <v>75</v>
+      </c>
+      <c r="B39" s="7">
+        <v>45593.675324074178583240102992</v>
+      </c>
+      <c r="C39" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D39" s="9">
+        <v>45593.677928240845249912738892</v>
+      </c>
+      <c r="E39" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F39" s="11">
+        <v>45593</v>
+      </c>
+      <c r="G39" s="12">
+        <v>553000</v>
+      </c>
+      <c r="H39" t="s" s="13">
         <v>76</v>
-      </c>
-      <c r="B39" s="7">
-        <v>45558.77800925936368843416568</v>
-      </c>
-      <c r="C39" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D39" s="9">
-        <v>45558.778252314919243990278364</v>
-      </c>
-      <c r="E39" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F39" s="11">
-        <v>45558</v>
-      </c>
-      <c r="G39" s="12">
-        <v>1000</v>
-      </c>
-      <c r="H39" t="s" s="13">
-        <v>77</v>
       </c>
       <c r="I39" t="s" s="14">
         <v>12</v>
@@ -2232,28 +2250,28 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="6">
+        <v>77</v>
+      </c>
+      <c r="B40" s="7">
+        <v>45558.77800925936368843416568</v>
+      </c>
+      <c r="C40" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D40" s="9">
+        <v>45558.778252314919243990278364</v>
+      </c>
+      <c r="E40" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F40" s="11">
+        <v>45558</v>
+      </c>
+      <c r="G40" s="12">
+        <v>1000</v>
+      </c>
+      <c r="H40" t="s" s="13">
         <v>78</v>
-      </c>
-      <c r="B40" s="7">
-        <v>45601.398993055660082425667292</v>
-      </c>
-      <c r="C40" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D40" s="9">
-        <v>45601.399606481586008352999304</v>
-      </c>
-      <c r="E40" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F40" s="11">
-        <v>45600</v>
-      </c>
-      <c r="G40" s="12">
-        <v>10000</v>
-      </c>
-      <c r="H40" t="s" s="13">
-        <v>79</v>
       </c>
       <c r="I40" t="s" s="14">
         <v>12</v>
@@ -2261,28 +2279,28 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="6">
+        <v>79</v>
+      </c>
+      <c r="B41" s="7">
+        <v>45601.398993055660082425667292</v>
+      </c>
+      <c r="C41" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D41" s="9">
+        <v>45601.399606481586008352999304</v>
+      </c>
+      <c r="E41" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F41" s="11">
+        <v>45600</v>
+      </c>
+      <c r="G41" s="12">
+        <v>10000</v>
+      </c>
+      <c r="H41" t="s" s="13">
         <v>80</v>
-      </c>
-      <c r="B41" s="7">
-        <v>45607.61944444454898557298528</v>
-      </c>
-      <c r="C41" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D41" s="9">
-        <v>45607.620104166771207796719708</v>
-      </c>
-      <c r="E41" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F41" s="11">
-        <v>45607</v>
-      </c>
-      <c r="G41" s="12">
-        <v>110000</v>
-      </c>
-      <c r="H41" t="s" s="13">
-        <v>81</v>
       </c>
       <c r="I41" t="s" s="14">
         <v>12</v>
@@ -2290,28 +2308,28 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="6">
+        <v>81</v>
+      </c>
+      <c r="B42" s="7">
+        <v>45607.61944444454898557298528</v>
+      </c>
+      <c r="C42" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D42" s="9">
+        <v>45607.620104166771207796719708</v>
+      </c>
+      <c r="E42" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F42" s="11">
+        <v>45607</v>
+      </c>
+      <c r="G42" s="12">
+        <v>110000</v>
+      </c>
+      <c r="H42" t="s" s="13">
         <v>82</v>
-      </c>
-      <c r="B42" s="7">
-        <v>45686.84988425936398199867332</v>
-      </c>
-      <c r="C42" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D42" s="9">
-        <v>45686.850277777882500518093856</v>
-      </c>
-      <c r="E42" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F42" s="11">
-        <v>45686</v>
-      </c>
-      <c r="G42" s="12">
-        <v>29000</v>
-      </c>
-      <c r="H42" t="s" s="13">
-        <v>83</v>
       </c>
       <c r="I42" t="s" s="14">
         <v>12</v>
@@ -2319,28 +2337,28 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="6">
+        <v>83</v>
+      </c>
+      <c r="B43" s="7">
+        <v>45686.84988425936398199867332</v>
+      </c>
+      <c r="C43" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D43" s="9">
+        <v>45686.850277777882500518093856</v>
+      </c>
+      <c r="E43" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F43" s="11">
+        <v>45686</v>
+      </c>
+      <c r="G43" s="12">
+        <v>29000</v>
+      </c>
+      <c r="H43" t="s" s="13">
         <v>84</v>
-      </c>
-      <c r="B43" s="7">
-        <v>45700.69583333343808781023248</v>
-      </c>
-      <c r="C43" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D43" s="9">
-        <v>45700.696041666771421144043352</v>
-      </c>
-      <c r="E43" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F43" s="11">
-        <v>45700</v>
-      </c>
-      <c r="G43" s="12">
-        <v>12000</v>
-      </c>
-      <c r="H43" t="s" s="13">
-        <v>85</v>
       </c>
       <c r="I43" t="s" s="14">
         <v>12</v>
@@ -2348,28 +2366,28 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="6">
+        <v>85</v>
+      </c>
+      <c r="B44" s="7">
+        <v>45700.69583333343808781023248</v>
+      </c>
+      <c r="C44" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D44" s="9">
+        <v>45700.696041666771421144043352</v>
+      </c>
+      <c r="E44" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F44" s="11">
+        <v>45700</v>
+      </c>
+      <c r="G44" s="12">
+        <v>12000</v>
+      </c>
+      <c r="H44" t="s" s="13">
         <v>86</v>
-      </c>
-      <c r="B44" s="7">
-        <v>45672.7210648149195051683524</v>
-      </c>
-      <c r="C44" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D44" s="9">
-        <v>45672.73130787047506074738694</v>
-      </c>
-      <c r="E44" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F44" s="11">
-        <v>45641</v>
-      </c>
-      <c r="G44" s="12">
-        <v>7500</v>
-      </c>
-      <c r="H44" t="s" s="13">
-        <v>87</v>
       </c>
       <c r="I44" t="s" s="14">
         <v>12</v>
@@ -2377,28 +2395,28 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="6">
+        <v>87</v>
+      </c>
+      <c r="B45" s="7">
+        <v>45672.7210648149195051683524</v>
+      </c>
+      <c r="C45" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D45" s="9">
+        <v>45672.73130787047506074738694</v>
+      </c>
+      <c r="E45" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F45" s="11">
+        <v>45641</v>
+      </c>
+      <c r="G45" s="12">
+        <v>7500</v>
+      </c>
+      <c r="H45" t="s" s="13">
         <v>88</v>
-      </c>
-      <c r="B45" s="7">
-        <v>45611.422881944548994291169948</v>
-      </c>
-      <c r="C45" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D45" s="9">
-        <v>45611.427916666771216524932688</v>
-      </c>
-      <c r="E45" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F45" s="11">
-        <v>45611</v>
-      </c>
-      <c r="G45" s="12">
-        <v>2000</v>
-      </c>
-      <c r="H45" t="s" s="13">
-        <v>89</v>
       </c>
       <c r="I45" t="s" s="14">
         <v>12</v>
@@ -2406,28 +2424,28 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="6">
+        <v>89</v>
+      </c>
+      <c r="B46" s="7">
+        <v>45611.422881944548994291169948</v>
+      </c>
+      <c r="C46" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D46" s="9">
+        <v>45611.427916666771216524932688</v>
+      </c>
+      <c r="E46" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F46" s="11">
+        <v>45611</v>
+      </c>
+      <c r="G46" s="12">
+        <v>2000</v>
+      </c>
+      <c r="H46" t="s" s="13">
         <v>90</v>
-      </c>
-      <c r="B46" s="7">
-        <v>45705.440636574178839426942884</v>
-      </c>
-      <c r="C46" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D46" s="9">
-        <v>45705.441053240845506094564628</v>
-      </c>
-      <c r="E46" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F46" s="11">
-        <v>45705</v>
-      </c>
-      <c r="G46" s="12">
-        <v>110000</v>
-      </c>
-      <c r="H46" t="s" s="13">
-        <v>11</v>
       </c>
       <c r="I46" t="s" s="14">
         <v>12</v>
@@ -2438,25 +2456,25 @@
         <v>91</v>
       </c>
       <c r="B47" s="7">
-        <v>45700.703831018623273013749844</v>
+        <v>45705.440636574178839426942884</v>
       </c>
       <c r="C47" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D47" s="9">
-        <v>45700.705289351956606350425948</v>
+        <v>45705.441053240845506094564628</v>
       </c>
       <c r="E47" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F47" s="11">
-        <v>45700</v>
+        <v>45705</v>
       </c>
       <c r="G47" s="12">
-        <v>2000</v>
+        <v>110000</v>
       </c>
       <c r="H47" t="s" s="13">
-        <v>92</v>
+        <v>11</v>
       </c>
       <c r="I47" t="s" s="14">
         <v>12</v>
@@ -2464,28 +2482,28 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="6">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B48" s="7">
-        <v>45594.72557870380821527711116</v>
+        <v>45700.703831018623273013749844</v>
       </c>
       <c r="C48" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D48" s="9">
-        <v>45594.72586805566006712962626</v>
+        <v>45700.705289351956606350425948</v>
       </c>
       <c r="E48" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F48" s="11">
-        <v>45594</v>
+        <v>45700</v>
       </c>
       <c r="G48" s="12">
         <v>2000</v>
       </c>
       <c r="H48" t="s" s="13">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="I48" t="s" s="14">
         <v>12</v>
@@ -2496,25 +2514,25 @@
         <v>94</v>
       </c>
       <c r="B49" s="7">
-        <v>45644.5865162038083295676341</v>
+        <v>45594.72557870380821527711116</v>
       </c>
       <c r="C49" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D49" s="9">
-        <v>45644.58831018528981105322772</v>
+        <v>45594.72586805566006712962626</v>
       </c>
       <c r="E49" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F49" s="11">
-        <v>45644</v>
+        <v>45594</v>
       </c>
       <c r="G49" s="12">
-        <v>14000</v>
+        <v>2000</v>
       </c>
       <c r="H49" t="s" s="13">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I49" t="s" s="14">
         <v>12</v>
@@ -2522,28 +2540,28 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="6">
+        <v>95</v>
+      </c>
+      <c r="B50" s="7">
+        <v>45644.5865162038083295676341</v>
+      </c>
+      <c r="C50" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D50" s="9">
+        <v>45644.58831018528981105322772</v>
+      </c>
+      <c r="E50" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F50" s="11">
+        <v>45644</v>
+      </c>
+      <c r="G50" s="12">
+        <v>14000</v>
+      </c>
+      <c r="H50" t="s" s="13">
         <v>96</v>
-      </c>
-      <c r="B50" s="7">
-        <v>45611.428078703808253562341144</v>
-      </c>
-      <c r="C50" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D50" s="9">
-        <v>45611.429236111215660972401544</v>
-      </c>
-      <c r="E50" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F50" s="11">
-        <v>45608</v>
-      </c>
-      <c r="G50" s="12">
-        <v>2000</v>
-      </c>
-      <c r="H50" t="s" s="13">
-        <v>97</v>
       </c>
       <c r="I50" t="s" s="14">
         <v>12</v>
@@ -2551,28 +2569,28 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="6">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B51" s="7">
-        <v>45680.67060185195656042720376</v>
+        <v>45611.428078703808253562341144</v>
       </c>
       <c r="C51" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D51" s="9">
-        <v>45680.670960648252856724322484</v>
+        <v>45611.429236111215660972401544</v>
       </c>
       <c r="E51" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F51" s="11">
-        <v>45680</v>
+        <v>45608</v>
       </c>
       <c r="G51" s="12">
         <v>2000</v>
       </c>
       <c r="H51" t="s" s="13">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="I51" t="s" s="14">
         <v>12</v>
@@ -2583,25 +2601,25 @@
         <v>99</v>
       </c>
       <c r="B52" s="7">
-        <v>45608.013981481586023514374432</v>
+        <v>45680.67060185195656042720376</v>
       </c>
       <c r="C52" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D52" s="9">
-        <v>45608.014398148252690181996176</v>
+        <v>45680.670960648252856724322484</v>
       </c>
       <c r="E52" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F52" s="11">
-        <v>45608</v>
+        <v>45680</v>
       </c>
       <c r="G52" s="12">
-        <v>5500</v>
+        <v>2000</v>
       </c>
       <c r="H52" t="s" s="13">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="I52" t="s" s="14">
         <v>12</v>
@@ -2609,28 +2627,28 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="6">
+        <v>100</v>
+      </c>
+      <c r="B53" s="7">
+        <v>45608.013981481586023514374432</v>
+      </c>
+      <c r="C53" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D53" s="9">
+        <v>45608.014398148252690181996176</v>
+      </c>
+      <c r="E53" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F53" s="11">
+        <v>45608</v>
+      </c>
+      <c r="G53" s="12">
+        <v>5500</v>
+      </c>
+      <c r="H53" t="s" s="13">
         <v>101</v>
-      </c>
-      <c r="B53" s="7">
-        <v>45593.658518518623027646025984</v>
-      </c>
-      <c r="C53" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D53" s="9">
-        <v>45593.658831018623027646742292</v>
-      </c>
-      <c r="E53" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F53" s="11">
-        <v>45590</v>
-      </c>
-      <c r="G53" s="12">
-        <v>1000</v>
-      </c>
-      <c r="H53" t="s" s="13">
-        <v>25</v>
       </c>
       <c r="I53" t="s" s="14">
         <v>12</v>
@@ -2641,25 +2659,25 @@
         <v>102</v>
       </c>
       <c r="B54" s="7">
-        <v>45611.422407407511957253045184</v>
+        <v>45593.658518518623027646025984</v>
       </c>
       <c r="C54" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D54" s="9">
-        <v>45611.422696759363809105560284</v>
+        <v>45593.658831018623027646742292</v>
       </c>
       <c r="E54" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F54" s="11">
-        <v>45611</v>
+        <v>45590</v>
       </c>
       <c r="G54" s="12">
-        <v>13000</v>
+        <v>1000</v>
       </c>
       <c r="H54" t="s" s="13">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="I54" t="s" s="14">
         <v>12</v>
@@ -2667,28 +2685,28 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="6">
+        <v>103</v>
+      </c>
+      <c r="B55" s="7">
+        <v>45611.422407407511957253045184</v>
+      </c>
+      <c r="C55" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D55" s="9">
+        <v>45611.422696759363809105560284</v>
+      </c>
+      <c r="E55" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F55" s="11">
+        <v>45611</v>
+      </c>
+      <c r="G55" s="12">
+        <v>13000</v>
+      </c>
+      <c r="H55" t="s" s="13">
         <v>104</v>
-      </c>
-      <c r="B55" s="7">
-        <v>45692.680335648252884252038924</v>
-      </c>
-      <c r="C55" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D55" s="9">
-        <v>45692.681412037141773143395096</v>
-      </c>
-      <c r="E55" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F55" s="11">
-        <v>45692</v>
-      </c>
-      <c r="G55" s="12">
-        <v>110000</v>
-      </c>
-      <c r="H55" t="s" s="13">
-        <v>11</v>
       </c>
       <c r="I55" t="s" s="14">
         <v>12</v>
@@ -2699,25 +2717,25 @@
         <v>105</v>
       </c>
       <c r="B56" s="7">
-        <v>45594.725104166771178238986396</v>
+        <v>45692.680335648252884252038924</v>
       </c>
       <c r="C56" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D56" s="9">
-        <v>45594.725439814919326387903912</v>
+        <v>45692.681412037141773143395096</v>
       </c>
       <c r="E56" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F56" s="11">
-        <v>45594</v>
+        <v>45692</v>
       </c>
       <c r="G56" s="12">
-        <v>5000</v>
+        <v>110000</v>
       </c>
       <c r="H56" t="s" s="13">
-        <v>106</v>
+        <v>11</v>
       </c>
       <c r="I56" t="s" s="14">
         <v>12</v>
@@ -2725,28 +2743,28 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="6">
+        <v>106</v>
+      </c>
+      <c r="B57" s="7">
+        <v>45594.725104166771178238986396</v>
+      </c>
+      <c r="C57" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D57" s="9">
+        <v>45594.725439814919326387903912</v>
+      </c>
+      <c r="E57" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F57" s="11">
+        <v>45594</v>
+      </c>
+      <c r="G57" s="12">
+        <v>5000</v>
+      </c>
+      <c r="H57" t="s" s="13">
         <v>107</v>
-      </c>
-      <c r="B57" s="7">
-        <v>45642.440821759363880204859748</v>
-      </c>
-      <c r="C57" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D57" s="9">
-        <v>45642.44160879640091724370082</v>
-      </c>
-      <c r="E57" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F57" s="11">
-        <v>45638</v>
-      </c>
-      <c r="G57" s="12">
-        <v>1000</v>
-      </c>
-      <c r="H57" t="s" s="13">
-        <v>25</v>
       </c>
       <c r="I57" t="s" s="14">
         <v>12</v>
@@ -2757,25 +2775,25 @@
         <v>108</v>
       </c>
       <c r="B58" s="7">
-        <v>45579.710810185289662341956456</v>
+        <v>45642.440821759363880204859748</v>
       </c>
       <c r="C58" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D58" s="9">
-        <v>45579.711087963067440120370952</v>
+        <v>45642.44160879640091724370082</v>
       </c>
       <c r="E58" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F58" s="11">
-        <v>45579</v>
+        <v>45638</v>
       </c>
       <c r="G58" s="12">
-        <v>95000</v>
+        <v>1000</v>
       </c>
       <c r="H58" t="s" s="13">
-        <v>109</v>
+        <v>25</v>
       </c>
       <c r="I58" t="s" s="14">
         <v>12</v>
@@ -2783,28 +2801,28 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="6">
+        <v>109</v>
+      </c>
+      <c r="B59" s="7">
+        <v>45579.710810185289662341956456</v>
+      </c>
+      <c r="C59" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D59" s="9">
+        <v>45579.711087963067440120370952</v>
+      </c>
+      <c r="E59" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F59" s="11">
+        <v>45579</v>
+      </c>
+      <c r="G59" s="12">
+        <v>95000</v>
+      </c>
+      <c r="H59" t="s" s="13">
         <v>110</v>
-      </c>
-      <c r="B59" s="7">
-        <v>45567.7352430556600052621043</v>
-      </c>
-      <c r="C59" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D59" s="9">
-        <v>45567.735914351956301559939332</v>
-      </c>
-      <c r="E59" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F59" s="11">
-        <v>45567</v>
-      </c>
-      <c r="G59" s="12">
-        <v>60000</v>
-      </c>
-      <c r="H59" t="s" s="13">
-        <v>111</v>
       </c>
       <c r="I59" t="s" s="14">
         <v>12</v>
@@ -2812,28 +2830,28 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="6">
+        <v>111</v>
+      </c>
+      <c r="B60" s="7">
+        <v>45567.7352430556600052621043</v>
+      </c>
+      <c r="C60" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D60" s="9">
+        <v>45567.735914351956301559939332</v>
+      </c>
+      <c r="E60" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F60" s="11">
+        <v>45567</v>
+      </c>
+      <c r="G60" s="12">
+        <v>60000</v>
+      </c>
+      <c r="H60" t="s" s="13">
         <v>112</v>
-      </c>
-      <c r="B60" s="7">
-        <v>45601.466076388993415912768076</v>
-      </c>
-      <c r="C60" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D60" s="9">
-        <v>45601.466932870474897396212772</v>
-      </c>
-      <c r="E60" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F60" s="11">
-        <v>45601</v>
-      </c>
-      <c r="G60" s="12">
-        <v>110000</v>
-      </c>
-      <c r="H60" t="s" s="13">
-        <v>11</v>
       </c>
       <c r="I60" t="s" s="14">
         <v>12</v>
@@ -2844,25 +2862,25 @@
         <v>113</v>
       </c>
       <c r="B61" s="7">
-        <v>45593.674571759363768423563732</v>
+        <v>45601.466076388993415912768076</v>
       </c>
       <c r="C61" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D61" s="9">
-        <v>45593.67517361121562027679514</v>
+        <v>45601.466932870474897396212772</v>
       </c>
       <c r="E61" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F61" s="11">
-        <v>45593</v>
+        <v>45601</v>
       </c>
       <c r="G61" s="12">
         <v>110000</v>
       </c>
       <c r="H61" t="s" s="13">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="I61" t="s" s="14">
         <v>12</v>
@@ -2873,25 +2891,25 @@
         <v>114</v>
       </c>
       <c r="B62" s="7">
-        <v>45663.483611111215780290690336</v>
+        <v>45593.674571759363768423563732</v>
       </c>
       <c r="C62" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D62" s="9">
-        <v>45663.485451388993558072686372</v>
+        <v>45593.67517361121562027679514</v>
       </c>
       <c r="E62" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F62" s="11">
-        <v>45653</v>
+        <v>45593</v>
       </c>
       <c r="G62" s="12">
-        <v>10000</v>
+        <v>110000</v>
       </c>
       <c r="H62" t="s" s="13">
-        <v>115</v>
+        <v>31</v>
       </c>
       <c r="I62" t="s" s="14">
         <v>12</v>
@@ -2899,28 +2917,28 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="6">
+        <v>115</v>
+      </c>
+      <c r="B63" s="7">
+        <v>45663.483611111215780290690336</v>
+      </c>
+      <c r="C63" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D63" s="9">
+        <v>45663.485451388993558072686372</v>
+      </c>
+      <c r="E63" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F63" s="11">
+        <v>45653</v>
+      </c>
+      <c r="G63" s="12">
+        <v>10000</v>
+      </c>
+      <c r="H63" t="s" s="13">
         <v>116</v>
-      </c>
-      <c r="B63" s="7">
-        <v>45635.658923611215716511342324</v>
-      </c>
-      <c r="C63" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D63" s="9">
-        <v>45635.664594907512012820638284</v>
-      </c>
-      <c r="E63" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F63" s="11">
-        <v>45635</v>
-      </c>
-      <c r="G63" s="12">
-        <v>110000</v>
-      </c>
-      <c r="H63" t="s" s="13">
-        <v>11</v>
       </c>
       <c r="I63" t="s" s="14">
         <v>12</v>
@@ -2931,25 +2949,25 @@
         <v>117</v>
       </c>
       <c r="B64" s="7">
-        <v>45699.698182870475122560469492</v>
+        <v>45635.658923611215716511342324</v>
       </c>
       <c r="C64" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D64" s="9">
-        <v>45699.698761574178826265499692</v>
+        <v>45635.664594907512012820638284</v>
       </c>
       <c r="E64" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F64" s="11">
-        <v>45692</v>
+        <v>45635</v>
       </c>
       <c r="G64" s="12">
-        <v>2000</v>
+        <v>110000</v>
       </c>
       <c r="H64" t="s" s="13">
-        <v>118</v>
+        <v>11</v>
       </c>
       <c r="I64" t="s" s="14">
         <v>12</v>
@@ -2957,28 +2975,28 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="6">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B65" s="7">
-        <v>45685.459745370475089923328088</v>
+        <v>45699.698182870475122560469492</v>
       </c>
       <c r="C65" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D65" s="9">
-        <v>45685.460138888993608442748624</v>
+        <v>45699.698761574178826265499692</v>
       </c>
       <c r="E65" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F65" s="11">
-        <v>45685</v>
+        <v>45692</v>
       </c>
       <c r="G65" s="12">
         <v>2000</v>
       </c>
       <c r="H65" t="s" s="13">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I65" t="s" s="14">
         <v>12</v>
@@ -2986,28 +3004,28 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="6">
+        <v>120</v>
+      </c>
+      <c r="B66" s="7">
+        <v>45685.459745370475089923328088</v>
+      </c>
+      <c r="C66" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D66" s="9">
+        <v>45685.460138888993608442748624</v>
+      </c>
+      <c r="E66" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F66" s="11">
+        <v>45685</v>
+      </c>
+      <c r="G66" s="12">
+        <v>2000</v>
+      </c>
+      <c r="H66" t="s" s="13">
         <v>121</v>
-      </c>
-      <c r="B66" s="7">
-        <v>45618.457453703808269674973296</v>
-      </c>
-      <c r="C66" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D66" s="9">
-        <v>45618.457708333437899305186584</v>
-      </c>
-      <c r="E66" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F66" s="11">
-        <v>45618</v>
-      </c>
-      <c r="G66" s="12">
-        <v>1000</v>
-      </c>
-      <c r="H66" t="s" s="13">
-        <v>122</v>
       </c>
       <c r="I66" t="s" s="14">
         <v>12</v>
@@ -3015,28 +3033,28 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="6">
+        <v>122</v>
+      </c>
+      <c r="B67" s="7">
+        <v>45618.457453703808269674973296</v>
+      </c>
+      <c r="C67" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D67" s="9">
+        <v>45618.457708333437899305186584</v>
+      </c>
+      <c r="E67" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F67" s="11">
+        <v>45618</v>
+      </c>
+      <c r="G67" s="12">
+        <v>1000</v>
+      </c>
+      <c r="H67" t="s" s="13">
         <v>123</v>
-      </c>
-      <c r="B67" s="7">
-        <v>45694.705995370475111117449192</v>
-      </c>
-      <c r="C67" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D67" s="9">
-        <v>45694.706342592697333340467312</v>
-      </c>
-      <c r="E67" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F67" s="11">
-        <v>45694</v>
-      </c>
-      <c r="G67" s="12">
-        <v>12000</v>
-      </c>
-      <c r="H67" t="s" s="13">
-        <v>124</v>
       </c>
       <c r="I67" t="s" s="14">
         <v>12</v>
@@ -3044,28 +3062,28 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="6">
+        <v>124</v>
+      </c>
+      <c r="B68" s="7">
+        <v>45694.705995370475111117449192</v>
+      </c>
+      <c r="C68" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D68" s="9">
+        <v>45694.706342592697333340467312</v>
+      </c>
+      <c r="E68" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F68" s="11">
+        <v>45694</v>
+      </c>
+      <c r="G68" s="12">
+        <v>12000</v>
+      </c>
+      <c r="H68" t="s" s="13">
         <v>125</v>
-      </c>
-      <c r="B68" s="7">
-        <v>45567.736087963067412671448392</v>
-      </c>
-      <c r="C68" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D68" s="9">
-        <v>45567.741562500104449721034084</v>
-      </c>
-      <c r="E68" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F68" s="11">
-        <v>45567</v>
-      </c>
-      <c r="G68" s="12">
-        <v>13000</v>
-      </c>
-      <c r="H68" t="s" s="13">
-        <v>103</v>
       </c>
       <c r="I68" t="s" s="14">
         <v>12</v>
@@ -3076,25 +3094,25 @@
         <v>126</v>
       </c>
       <c r="B69" s="7">
-        <v>45587.187395833437827627826564</v>
+        <v>45567.736087963067412671448392</v>
       </c>
       <c r="C69" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D69" s="9">
-        <v>45587.18796296306745725875616</v>
+        <v>45567.741562500104449721034084</v>
       </c>
       <c r="E69" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F69" s="11">
-        <v>45587</v>
+        <v>45567</v>
       </c>
       <c r="G69" s="12">
-        <v>100000</v>
+        <v>13000</v>
       </c>
       <c r="H69" t="s" s="13">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="I69" t="s" s="14">
         <v>12</v>
@@ -3105,25 +3123,25 @@
         <v>127</v>
       </c>
       <c r="B70" s="7">
-        <v>45593.659189814919323943861016</v>
+        <v>45713.649027777882561945802704</v>
       </c>
       <c r="C70" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D70" s="9">
-        <v>45593.660462963067472094927456</v>
+        <v>45713.649583333438117502631696</v>
       </c>
       <c r="E70" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F70" s="11">
-        <v>45589</v>
+        <v>45713</v>
       </c>
       <c r="G70" s="12">
-        <v>7200</v>
+        <v>110000</v>
       </c>
       <c r="H70" t="s" s="13">
-        <v>128</v>
+        <v>11</v>
       </c>
       <c r="I70" t="s" s="14">
         <v>12</v>
@@ -3131,28 +3149,28 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="6">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B71" s="7">
-        <v>45622.691458333437909009727368</v>
+        <v>45587.187395833437827627826564</v>
       </c>
       <c r="C71" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D71" s="9">
-        <v>45622.699733796400871991659228</v>
+        <v>45587.18796296306745725875616</v>
       </c>
       <c r="E71" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F71" s="11">
-        <v>45622</v>
+        <v>45587</v>
       </c>
       <c r="G71" s="12">
-        <v>2000</v>
+        <v>100000</v>
       </c>
       <c r="H71" t="s" s="13">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="I71" t="s" s="14">
         <v>12</v>
@@ -3160,28 +3178,28 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="6">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B72" s="7">
-        <v>45567.756689814919264570523512</v>
+        <v>45593.659189814919323943861016</v>
       </c>
       <c r="C72" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D72" s="9">
-        <v>45567.757083333437783089944048</v>
+        <v>45593.660462963067472094927456</v>
       </c>
       <c r="E72" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F72" s="11">
-        <v>45561</v>
+        <v>45589</v>
       </c>
       <c r="G72" s="12">
-        <v>33000</v>
+        <v>7200</v>
       </c>
       <c r="H72" t="s" s="13">
-        <v>68</v>
+        <v>130</v>
       </c>
       <c r="I72" t="s" s="14">
         <v>12</v>
@@ -3189,28 +3207,28 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="6">
+        <v>131</v>
+      </c>
+      <c r="B73" s="7">
+        <v>45622.691458333437909009727368</v>
+      </c>
+      <c r="C73" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D73" s="9">
+        <v>45622.699733796400871991659228</v>
+      </c>
+      <c r="E73" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F73" s="11">
+        <v>45622</v>
+      </c>
+      <c r="G73" s="12">
+        <v>2000</v>
+      </c>
+      <c r="H73" t="s" s="13">
         <v>132</v>
-      </c>
-      <c r="B73" s="7">
-        <v>45600.499340277882302585718372</v>
-      </c>
-      <c r="C73" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D73" s="9">
-        <v>45600.499988426030450735352196</v>
-      </c>
-      <c r="E73" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F73" s="11">
-        <v>45600</v>
-      </c>
-      <c r="G73" s="12">
-        <v>40000</v>
-      </c>
-      <c r="H73" t="s" s="13">
-        <v>133</v>
       </c>
       <c r="I73" t="s" s="14">
         <v>12</v>
@@ -3218,28 +3236,28 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="6">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B74" s="7">
-        <v>45632.696458333437931943044296</v>
+        <v>45567.756689814919264570523512</v>
       </c>
       <c r="C74" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D74" s="9">
-        <v>45632.697083333437931944476912</v>
+        <v>45567.757083333437783089944048</v>
       </c>
       <c r="E74" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F74" s="11">
-        <v>45628</v>
+        <v>45561</v>
       </c>
       <c r="G74" s="12">
-        <v>5000</v>
+        <v>33000</v>
       </c>
       <c r="H74" t="s" s="13">
-        <v>135</v>
+        <v>69</v>
       </c>
       <c r="I74" t="s" s="14">
         <v>12</v>
@@ -3247,28 +3265,28 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="6">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B75" s="7">
-        <v>45574.63807870380816923283292</v>
+        <v>45600.499340277882302585718372</v>
       </c>
       <c r="C75" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D75" s="9">
-        <v>45574.640486111215576645758552</v>
+        <v>45600.499988426030450735352196</v>
       </c>
       <c r="E75" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F75" s="11">
-        <v>45553</v>
+        <v>45600</v>
       </c>
       <c r="G75" s="12">
-        <v>47500</v>
+        <v>40000</v>
       </c>
       <c r="H75" t="s" s="13">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I75" t="s" s="14">
         <v>12</v>
@@ -3276,28 +3294,28 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="6">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B76" s="7">
-        <v>45694.706932870475111119598116</v>
+        <v>45632.696458333437931943044296</v>
       </c>
       <c r="C76" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D76" s="9">
-        <v>45694.721863426030666709377276</v>
+        <v>45632.697083333437931944476912</v>
       </c>
       <c r="E76" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F76" s="11">
-        <v>45694</v>
+        <v>45628</v>
       </c>
       <c r="G76" s="12">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="H76" t="s" s="13">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I76" t="s" s="14">
         <v>12</v>
@@ -3305,28 +3323,28 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="6">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B77" s="7">
-        <v>45700.691388888993643355600544</v>
+        <v>45574.63807870380816923283292</v>
       </c>
       <c r="C77" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D77" s="9">
-        <v>45700.694525463067717436864228</v>
+        <v>45574.640486111215576645758552</v>
       </c>
       <c r="E77" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F77" s="11">
-        <v>45672</v>
+        <v>45553</v>
       </c>
       <c r="G77" s="12">
-        <v>5000</v>
+        <v>47500</v>
       </c>
       <c r="H77" t="s" s="13">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I77" t="s" s="14">
         <v>12</v>
@@ -3334,28 +3352,28 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="6">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B78" s="7">
-        <v>45663.49039351862318771364428</v>
+        <v>45694.706932870475111119598116</v>
       </c>
       <c r="C78" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D78" s="9">
-        <v>45663.490868055660224751769044</v>
+        <v>45694.721863426030666709377276</v>
       </c>
       <c r="E78" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F78" s="11">
-        <v>45646</v>
+        <v>45694</v>
       </c>
       <c r="G78" s="12">
-        <v>6500</v>
+        <v>1000</v>
       </c>
       <c r="H78" t="s" s="13">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="I78" t="s" s="14">
         <v>12</v>
@@ -3363,28 +3381,28 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="6">
+        <v>142</v>
+      </c>
+      <c r="B79" s="7">
+        <v>45700.691388888993643355600544</v>
+      </c>
+      <c r="C79" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D79" s="9">
+        <v>45700.694525463067717436864228</v>
+      </c>
+      <c r="E79" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F79" s="11">
+        <v>45672</v>
+      </c>
+      <c r="G79" s="12">
+        <v>5000</v>
+      </c>
+      <c r="H79" t="s" s="13">
         <v>143</v>
-      </c>
-      <c r="B79" s="7">
-        <v>45700.696689814919569293677176</v>
-      </c>
-      <c r="C79" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D79" s="9">
-        <v>45700.696956018623272997991068</v>
-      </c>
-      <c r="E79" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F79" s="11">
-        <v>45699</v>
-      </c>
-      <c r="G79" s="12">
-        <v>1000</v>
-      </c>
-      <c r="H79" t="s" s="13">
-        <v>25</v>
       </c>
       <c r="I79" t="s" s="14">
         <v>12</v>
@@ -3395,25 +3413,25 @@
         <v>144</v>
       </c>
       <c r="B80" s="7">
-        <v>45594.727824074178585652628336</v>
+        <v>45663.49039351862318771364428</v>
       </c>
       <c r="C80" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D80" s="9">
-        <v>45594.728344907511918987155516</v>
+        <v>45663.490868055660224751769044</v>
       </c>
       <c r="E80" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F80" s="11">
-        <v>45590</v>
+        <v>45646</v>
       </c>
       <c r="G80" s="12">
-        <v>13000</v>
+        <v>6500</v>
       </c>
       <c r="H80" t="s" s="13">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I80" t="s" s="14">
         <v>12</v>
@@ -3424,25 +3442,25 @@
         <v>145</v>
       </c>
       <c r="B81" s="7">
-        <v>45567.73454861121556081606806</v>
+        <v>45700.696689814919569293677176</v>
       </c>
       <c r="C81" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D81" s="9">
-        <v>45567.734803240845190446281348</v>
+        <v>45700.696956018623272997991068</v>
       </c>
       <c r="E81" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F81" s="11">
-        <v>45567</v>
+        <v>45699</v>
       </c>
       <c r="G81" s="12">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="H81" t="s" s="13">
-        <v>146</v>
+        <v>25</v>
       </c>
       <c r="I81" t="s" s="14">
         <v>12</v>
@@ -3450,28 +3468,28 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="6">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B82" s="7">
-        <v>45593.657129629734138753953504</v>
+        <v>45594.727824074178585652628336</v>
       </c>
       <c r="C82" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D82" s="9">
-        <v>45593.65787037047487949639216</v>
+        <v>45594.728344907511918987155516</v>
       </c>
       <c r="E82" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F82" s="11">
-        <v>45587</v>
+        <v>45590</v>
       </c>
       <c r="G82" s="12">
-        <v>1000</v>
+        <v>13000</v>
       </c>
       <c r="H82" t="s" s="13">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="I82" t="s" s="14">
         <v>12</v>
@@ -3479,28 +3497,28 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="6">
+        <v>147</v>
+      </c>
+      <c r="B83" s="7">
+        <v>45567.73454861121556081606806</v>
+      </c>
+      <c r="C83" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D83" s="9">
+        <v>45567.734803240845190446281348</v>
+      </c>
+      <c r="E83" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F83" s="11">
+        <v>45567</v>
+      </c>
+      <c r="G83" s="12">
+        <v>1500</v>
+      </c>
+      <c r="H83" t="s" s="13">
         <v>148</v>
-      </c>
-      <c r="B83" s="7">
-        <v>45600.500150463067487772760652</v>
-      </c>
-      <c r="C83" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D83" s="9">
-        <v>45600.50121527788230259001622</v>
-      </c>
-      <c r="E83" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F83" s="11">
-        <v>45600</v>
-      </c>
-      <c r="G83" s="12">
-        <v>35000</v>
-      </c>
-      <c r="H83" t="s" s="13">
-        <v>149</v>
       </c>
       <c r="I83" t="s" s="14">
         <v>12</v>
@@ -3508,28 +3526,28 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="6">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B84" s="7">
-        <v>45636.622766203808311313241028</v>
+        <v>45593.657129629734138753953504</v>
       </c>
       <c r="C84" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D84" s="9">
-        <v>45636.62349537047497798157908</v>
+        <v>45593.65787037047487949639216</v>
       </c>
       <c r="E84" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F84" s="11">
-        <v>45627</v>
+        <v>45587</v>
       </c>
       <c r="G84" s="12">
-        <v>25000</v>
+        <v>1000</v>
       </c>
       <c r="H84" t="s" s="13">
-        <v>151</v>
+        <v>25</v>
       </c>
       <c r="I84" t="s" s="14">
         <v>12</v>
@@ -3537,28 +3555,28 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="6">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B85" s="7">
-        <v>45593.661527777882286912183024</v>
+        <v>45600.500150463067487772760652</v>
       </c>
       <c r="C85" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D85" s="9">
-        <v>45593.665995370474879515016168</v>
+        <v>45600.50121527788230259001622</v>
       </c>
       <c r="E85" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F85" s="11">
-        <v>45593</v>
+        <v>45600</v>
       </c>
       <c r="G85" s="12">
-        <v>40500</v>
+        <v>35000</v>
       </c>
       <c r="H85" t="s" s="13">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I85" t="s" s="14">
         <v>12</v>
@@ -3566,28 +3584,28 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="6">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B86" s="7">
-        <v>45622.690011574178649747151868</v>
+        <v>45636.622766203808311313241028</v>
       </c>
       <c r="C86" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D86" s="9">
-        <v>45622.690370370474946044270592</v>
+        <v>45636.62349537047497798157908</v>
       </c>
       <c r="E86" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F86" s="11">
-        <v>45622</v>
+        <v>45627</v>
       </c>
       <c r="G86" s="12">
-        <v>2000</v>
+        <v>25000</v>
       </c>
       <c r="H86" t="s" s="13">
-        <v>92</v>
+        <v>153</v>
       </c>
       <c r="I86" t="s" s="14">
         <v>12</v>
@@ -3595,28 +3613,28 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="6">
+        <v>154</v>
+      </c>
+      <c r="B87" s="7">
+        <v>45593.661527777882286912183024</v>
+      </c>
+      <c r="C87" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D87" s="9">
+        <v>45593.665995370474879515016168</v>
+      </c>
+      <c r="E87" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F87" s="11">
+        <v>45593</v>
+      </c>
+      <c r="G87" s="12">
+        <v>40500</v>
+      </c>
+      <c r="H87" t="s" s="13">
         <v>155</v>
-      </c>
-      <c r="B87" s="7">
-        <v>45567.871076388993338906792844</v>
-      </c>
-      <c r="C87" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D87" s="9">
-        <v>45567.871423611215561129810964</v>
-      </c>
-      <c r="E87" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F87" s="11">
-        <v>45567</v>
-      </c>
-      <c r="G87" s="12">
-        <v>802380</v>
-      </c>
-      <c r="H87" t="s" s="13">
-        <v>156</v>
       </c>
       <c r="I87" t="s" s="14">
         <v>12</v>
@@ -3624,28 +3642,28 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="6">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B88" s="7">
-        <v>45685.459178240845460292398492</v>
+        <v>45622.690011574178649747151868</v>
       </c>
       <c r="C88" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D88" s="9">
-        <v>45685.459456018623238070812988</v>
+        <v>45622.690370370474946044270592</v>
       </c>
       <c r="E88" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F88" s="11">
-        <v>45685</v>
+        <v>45622</v>
       </c>
       <c r="G88" s="12">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="H88" t="s" s="13">
-        <v>158</v>
+        <v>93</v>
       </c>
       <c r="I88" t="s" s="14">
         <v>12</v>
@@ -3653,28 +3671,28 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="6">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B89" s="7">
-        <v>45687.727800926030650677687928</v>
+        <v>45567.871076388993338906792844</v>
       </c>
       <c r="C89" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D89" s="9">
-        <v>45687.728148148252872900706048</v>
+        <v>45567.871423611215561129810964</v>
       </c>
       <c r="E89" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F89" s="11">
-        <v>45687</v>
+        <v>45567</v>
       </c>
       <c r="G89" s="12">
-        <v>12500</v>
+        <v>802380</v>
       </c>
       <c r="H89" t="s" s="13">
-        <v>103</v>
+        <v>158</v>
       </c>
       <c r="I89" t="s" s="14">
         <v>12</v>
@@ -3682,28 +3700,28 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="6">
+        <v>159</v>
+      </c>
+      <c r="B90" s="7">
+        <v>45685.459178240845460292398492</v>
+      </c>
+      <c r="C90" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D90" s="9">
+        <v>45685.459456018623238070812988</v>
+      </c>
+      <c r="E90" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F90" s="11">
+        <v>45685</v>
+      </c>
+      <c r="G90" s="12">
+        <v>20000</v>
+      </c>
+      <c r="H90" t="s" s="13">
         <v>160</v>
-      </c>
-      <c r="B90" s="7">
-        <v>45665.579652777882451761873528</v>
-      </c>
-      <c r="C90" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D90" s="9">
-        <v>45665.586493055660229555330492</v>
-      </c>
-      <c r="E90" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F90" s="11">
-        <v>45665</v>
-      </c>
-      <c r="G90" s="12">
-        <v>6000</v>
-      </c>
-      <c r="H90" t="s" s="13">
-        <v>103</v>
       </c>
       <c r="I90" t="s" s="14">
         <v>12</v>
@@ -3714,25 +3732,25 @@
         <v>161</v>
       </c>
       <c r="B91" s="7">
-        <v>45700.017569444549197366636872</v>
+        <v>45687.727800926030650677687928</v>
       </c>
       <c r="C91" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D91" s="9">
-        <v>45700.018009259364012182459824</v>
+        <v>45687.728148148252872900706048</v>
       </c>
       <c r="E91" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F91" s="11">
-        <v>45700</v>
+        <v>45687</v>
       </c>
       <c r="G91" s="12">
-        <v>6000</v>
+        <v>12500</v>
       </c>
       <c r="H91" t="s" s="13">
-        <v>162</v>
+        <v>104</v>
       </c>
       <c r="I91" t="s" s="14">
         <v>12</v>
@@ -3740,28 +3758,28 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="6">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B92" s="7">
-        <v>45600.498391203808228509468844</v>
+        <v>45665.579652777882451761873528</v>
       </c>
       <c r="C92" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D92" s="9">
-        <v>45600.498645833437858139682132</v>
+        <v>45665.586493055660229555330492</v>
       </c>
       <c r="E92" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F92" s="11">
-        <v>45600</v>
+        <v>45665</v>
       </c>
       <c r="G92" s="12">
-        <v>500</v>
+        <v>6000</v>
       </c>
       <c r="H92" t="s" s="13">
-        <v>164</v>
+        <v>104</v>
       </c>
       <c r="I92" t="s" s="14">
         <v>12</v>
@@ -3769,28 +3787,28 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="6">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B93" s="7">
-        <v>45694.723171296401037082745528</v>
+        <v>45700.017569444549197366636872</v>
       </c>
       <c r="C93" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D93" s="9">
-        <v>45694.723506944549185231663044</v>
+        <v>45700.018009259364012182459824</v>
       </c>
       <c r="E93" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F93" s="11">
-        <v>45694</v>
+        <v>45700</v>
       </c>
       <c r="G93" s="12">
-        <v>30500</v>
+        <v>6000</v>
       </c>
       <c r="H93" t="s" s="13">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I93" t="s" s="14">
         <v>12</v>
@@ -3798,28 +3816,28 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="6">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B94" s="7">
-        <v>45594.728576388993400469167596</v>
+        <v>45600.498391203808228509468844</v>
       </c>
       <c r="C94" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D94" s="9">
-        <v>45594.728912037141548618085112</v>
+        <v>45600.498645833437858139682132</v>
       </c>
       <c r="E94" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F94" s="11">
-        <v>45594</v>
+        <v>45600</v>
       </c>
       <c r="G94" s="12">
-        <v>15000</v>
+        <v>500</v>
       </c>
       <c r="H94" t="s" s="13">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I94" t="s" s="14">
         <v>12</v>
@@ -3827,28 +3845,28 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="6">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B95" s="7">
-        <v>45601.398356481586008350134072</v>
+        <v>45694.723171296401037082745528</v>
       </c>
       <c r="C95" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D95" s="9">
-        <v>45601.398715277882304647252796</v>
+        <v>45694.723506944549185231663044</v>
       </c>
       <c r="E95" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F95" s="11">
-        <v>45601</v>
+        <v>45694</v>
       </c>
       <c r="G95" s="12">
-        <v>500</v>
+        <v>30500</v>
       </c>
       <c r="H95" t="s" s="13">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I95" t="s" s="14">
         <v>12</v>
@@ -3856,28 +3874,28 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="6">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B96" s="7">
-        <v>45618.71736111121567767813672</v>
+        <v>45594.728576388993400469167596</v>
       </c>
       <c r="C96" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D96" s="9">
-        <v>45618.7175925926971591601488</v>
+        <v>45594.728912037141548618085112</v>
       </c>
       <c r="E96" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F96" s="11">
-        <v>45618</v>
+        <v>45594</v>
       </c>
       <c r="G96" s="12">
-        <v>9000</v>
+        <v>15000</v>
       </c>
       <c r="H96" t="s" s="13">
-        <v>29</v>
+        <v>170</v>
       </c>
       <c r="I96" t="s" s="14">
         <v>12</v>
@@ -3885,28 +3903,28 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="6">
+        <v>171</v>
+      </c>
+      <c r="B97" s="7">
+        <v>45601.398356481586008350134072</v>
+      </c>
+      <c r="C97" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D97" s="9">
+        <v>45601.398715277882304647252796</v>
+      </c>
+      <c r="E97" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F97" s="11">
+        <v>45601</v>
+      </c>
+      <c r="G97" s="12">
+        <v>500</v>
+      </c>
+      <c r="H97" t="s" s="13">
         <v>172</v>
-      </c>
-      <c r="B97" s="7">
-        <v>45572.728148148252609299362048</v>
-      </c>
-      <c r="C97" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D97" s="9">
-        <v>45572.728437500104461151877148</v>
-      </c>
-      <c r="E97" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F97" s="11">
-        <v>45572</v>
-      </c>
-      <c r="G97" s="12">
-        <v>1000</v>
-      </c>
-      <c r="H97" t="s" s="13">
-        <v>56</v>
       </c>
       <c r="I97" t="s" s="14">
         <v>12</v>
@@ -3917,22 +3935,22 @@
         <v>173</v>
       </c>
       <c r="B98" s="7">
-        <v>45632.702962963067561587583744</v>
+        <v>45618.71736111121567767813672</v>
       </c>
       <c r="C98" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D98" s="9">
-        <v>45632.703344907512006032903676</v>
+        <v>45618.7175925926971591601488</v>
       </c>
       <c r="E98" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F98" s="11">
-        <v>45632</v>
+        <v>45618</v>
       </c>
       <c r="G98" s="12">
-        <v>10000</v>
+        <v>9000</v>
       </c>
       <c r="H98" t="s" s="13">
         <v>29</v>
@@ -3946,25 +3964,25 @@
         <v>174</v>
       </c>
       <c r="B99" s="7">
-        <v>45593.660601851956360984134704</v>
+        <v>45572.728148148252609299362048</v>
       </c>
       <c r="C99" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D99" s="9">
-        <v>45593.661354166771175800673964</v>
+        <v>45572.728437500104461151877148</v>
       </c>
       <c r="E99" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F99" s="11">
-        <v>45590</v>
+        <v>45572</v>
       </c>
       <c r="G99" s="12">
-        <v>34300</v>
+        <v>1000</v>
       </c>
       <c r="H99" t="s" s="13">
-        <v>175</v>
+        <v>56</v>
       </c>
       <c r="I99" t="s" s="14">
         <v>12</v>
@@ -3972,28 +3990,28 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="6">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B100" s="7">
-        <v>45629.62667824084533231394598</v>
+        <v>45632.702962963067561587583744</v>
       </c>
       <c r="C100" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D100" s="9">
-        <v>45629.627129629734221203869536</v>
+        <v>45632.703344907512006032903676</v>
       </c>
       <c r="E100" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F100" s="11">
-        <v>45629</v>
+        <v>45632</v>
       </c>
       <c r="G100" s="12">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="H100" t="s" s="13">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="I100" t="s" s="14">
         <v>12</v>
@@ -4001,28 +4019,28 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="6">
+        <v>176</v>
+      </c>
+      <c r="B101" s="7">
+        <v>45593.660601851956360984134704</v>
+      </c>
+      <c r="C101" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D101" s="9">
+        <v>45593.661354166771175800673964</v>
+      </c>
+      <c r="E101" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F101" s="11">
+        <v>45590</v>
+      </c>
+      <c r="G101" s="12">
+        <v>34300</v>
+      </c>
+      <c r="H101" t="s" s="13">
         <v>177</v>
-      </c>
-      <c r="B101" s="7">
-        <v>45558.776226851956281022672664</v>
-      </c>
-      <c r="C101" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D101" s="9">
-        <v>45558.777685185289614359348768</v>
-      </c>
-      <c r="E101" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F101" s="11">
-        <v>45558</v>
-      </c>
-      <c r="G101" s="12">
-        <v>39500</v>
-      </c>
-      <c r="H101" t="s" s="13">
-        <v>178</v>
       </c>
       <c r="I101" t="s" s="14">
         <v>12</v>
@@ -4030,28 +4048,28 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="6">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B102" s="7">
-        <v>45680.66892361121581968261618</v>
+        <v>45629.62667824084533231394598</v>
       </c>
       <c r="C102" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D102" s="9">
-        <v>45680.669224537141745609231884</v>
+        <v>45629.627129629734221203869536</v>
       </c>
       <c r="E102" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F102" s="11">
-        <v>45680</v>
+        <v>45629</v>
       </c>
       <c r="G102" s="12">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="H102" t="s" s="13">
-        <v>180</v>
+        <v>93</v>
       </c>
       <c r="I102" t="s" s="14">
         <v>12</v>
@@ -4059,28 +4077,28 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="6">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B103" s="7">
-        <v>45630.499733796400889870706908</v>
+        <v>45558.776226851956281022672664</v>
       </c>
       <c r="C103" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D103" s="9">
-        <v>45630.499976851956445426819592</v>
+        <v>45558.777685185289614359348768</v>
       </c>
       <c r="E103" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F103" s="11">
-        <v>45630</v>
+        <v>45558</v>
       </c>
       <c r="G103" s="12">
-        <v>20000</v>
+        <v>39500</v>
       </c>
       <c r="H103" t="s" s="13">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I103" t="s" s="14">
         <v>12</v>
@@ -4088,28 +4106,28 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="6">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B104" s="7">
-        <v>45594.727326388993400466302364</v>
+        <v>45680.66892361121581968261618</v>
       </c>
       <c r="C104" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D104" s="9">
-        <v>45594.727627314919326392918068</v>
+        <v>45680.669224537141745609231884</v>
       </c>
       <c r="E104" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F104" s="11">
-        <v>45581</v>
+        <v>45680</v>
       </c>
       <c r="G104" s="12">
-        <v>13000</v>
+        <v>5000</v>
       </c>
       <c r="H104" t="s" s="13">
-        <v>103</v>
+        <v>182</v>
       </c>
       <c r="I104" t="s" s="14">
         <v>12</v>
@@ -4117,28 +4135,28 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="6">
+        <v>183</v>
+      </c>
+      <c r="B105" s="7">
+        <v>45630.499733796400889870706908</v>
+      </c>
+      <c r="C105" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D105" s="9">
+        <v>45630.499976851956445426819592</v>
+      </c>
+      <c r="E105" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F105" s="11">
+        <v>45630</v>
+      </c>
+      <c r="G105" s="12">
+        <v>20000</v>
+      </c>
+      <c r="H105" t="s" s="13">
         <v>184</v>
-      </c>
-      <c r="B105" s="7">
-        <v>45600.676875000104525214883128</v>
-      </c>
-      <c r="C105" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D105" s="9">
-        <v>45600.677187500104525215599436</v>
-      </c>
-      <c r="E105" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F105" s="11">
-        <v>45600</v>
-      </c>
-      <c r="G105" s="12">
-        <v>6000</v>
-      </c>
-      <c r="H105" t="s" s="13">
-        <v>185</v>
       </c>
       <c r="I105" t="s" s="14">
         <v>12</v>
@@ -4146,28 +4164,28 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="6">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B106" s="7">
-        <v>45618.458530092697158566329468</v>
+        <v>45594.727326388993400466302364</v>
       </c>
       <c r="C106" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D106" s="9">
-        <v>45618.459050926030491900856648</v>
+        <v>45594.727627314919326392918068</v>
       </c>
       <c r="E106" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F106" s="11">
-        <v>45618</v>
+        <v>45581</v>
       </c>
       <c r="G106" s="12">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="H106" t="s" s="13">
-        <v>187</v>
+        <v>104</v>
       </c>
       <c r="I106" t="s" s="14">
         <v>12</v>
@@ -4175,28 +4193,28 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="6">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B107" s="7">
-        <v>45558.775416666771095835630384</v>
+        <v>45600.676875000104525214883128</v>
       </c>
       <c r="C107" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D107" s="9">
-        <v>45558.775891203808132873755148</v>
+        <v>45600.677187500104525215599436</v>
       </c>
       <c r="E107" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F107" s="11">
-        <v>45558</v>
+        <v>45600</v>
       </c>
       <c r="G107" s="12">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="H107" t="s" s="13">
-        <v>56</v>
+        <v>187</v>
       </c>
       <c r="I107" t="s" s="14">
         <v>12</v>
@@ -4204,28 +4222,28 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="6">
+        <v>188</v>
+      </c>
+      <c r="B108" s="7">
+        <v>45618.458530092697158566329468</v>
+      </c>
+      <c r="C108" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D108" s="9">
+        <v>45618.459050926030491900856648</v>
+      </c>
+      <c r="E108" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F108" s="11">
+        <v>45618</v>
+      </c>
+      <c r="G108" s="12">
+        <v>2000</v>
+      </c>
+      <c r="H108" t="s" s="13">
         <v>189</v>
-      </c>
-      <c r="B108" s="7">
-        <v>45567.871956018622968538438748</v>
-      </c>
-      <c r="C108" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D108" s="9">
-        <v>45567.872615740845190762173176</v>
-      </c>
-      <c r="E108" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F108" s="11">
-        <v>45567</v>
-      </c>
-      <c r="G108" s="12">
-        <v>1297075</v>
-      </c>
-      <c r="H108" t="s" s="13">
-        <v>190</v>
       </c>
       <c r="I108" t="s" s="14">
         <v>12</v>
@@ -4233,28 +4251,28 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="6">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B109" s="7">
-        <v>45567.734004629734079333339672</v>
+        <v>45558.775416666771095835630384</v>
       </c>
       <c r="C109" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D109" s="9">
-        <v>45567.73443287047482007506202</v>
+        <v>45558.775891203808132873755148</v>
       </c>
       <c r="E109" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F109" s="11">
-        <v>45567</v>
+        <v>45558</v>
       </c>
       <c r="G109" s="12">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="H109" t="s" s="13">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="I109" t="s" s="14">
         <v>12</v>
@@ -4262,28 +4280,28 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="6">
+        <v>191</v>
+      </c>
+      <c r="B110" s="7">
+        <v>45567.871956018622968538438748</v>
+      </c>
+      <c r="C110" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D110" s="9">
+        <v>45567.872615740845190762173176</v>
+      </c>
+      <c r="E110" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F110" s="11">
+        <v>45567</v>
+      </c>
+      <c r="G110" s="12">
+        <v>1297075</v>
+      </c>
+      <c r="H110" t="s" s="13">
         <v>192</v>
-      </c>
-      <c r="B110" s="7">
-        <v>45678.142557870475073150976268</v>
-      </c>
-      <c r="C110" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D110" s="9">
-        <v>45678.143622685289887968231836</v>
-      </c>
-      <c r="E110" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F110" s="11">
-        <v>45678</v>
-      </c>
-      <c r="G110" s="12">
-        <v>40000</v>
-      </c>
-      <c r="H110" t="s" s="13">
-        <v>193</v>
       </c>
       <c r="I110" t="s" s="14">
         <v>12</v>
@@ -4291,28 +4309,28 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="6">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B111" s="7">
-        <v>45579.715833333437810501618592</v>
+        <v>45567.734004629734079333339672</v>
       </c>
       <c r="C111" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D111" s="9">
-        <v>45579.716469907511884577151812</v>
+        <v>45567.73443287047482007506202</v>
       </c>
       <c r="E111" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F111" s="11">
-        <v>45579</v>
+        <v>45567</v>
       </c>
       <c r="G111" s="12">
-        <v>265600</v>
+        <v>2000</v>
       </c>
       <c r="H111" t="s" s="13">
-        <v>195</v>
+        <v>25</v>
       </c>
       <c r="I111" t="s" s="14">
         <v>12</v>
@@ -4320,28 +4338,28 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="6">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B112" s="7">
-        <v>45593.673831018623027681125076</v>
+        <v>45678.142557870475073150976268</v>
       </c>
       <c r="C112" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D112" s="9">
-        <v>45593.674166666771175830042592</v>
+        <v>45678.143622685289887968231836</v>
       </c>
       <c r="E112" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F112" s="11">
-        <v>45590</v>
+        <v>45678</v>
       </c>
       <c r="G112" s="12">
-        <v>76400</v>
+        <v>40000</v>
       </c>
       <c r="H112" t="s" s="13">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I112" t="s" s="14">
         <v>12</v>
@@ -4349,28 +4367,28 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="6">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B113" s="7">
-        <v>45708.645520833438106032391692</v>
+        <v>45579.715833333437810501618592</v>
       </c>
       <c r="C113" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D113" s="9">
-        <v>45708.652118055660328269735972</v>
+        <v>45579.716469907511884577151812</v>
       </c>
       <c r="E113" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F113" s="11">
-        <v>45708</v>
+        <v>45579</v>
       </c>
       <c r="G113" s="12">
-        <v>4000</v>
+        <v>265600</v>
       </c>
       <c r="H113" t="s" s="13">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I113" t="s" s="14">
         <v>12</v>
@@ -4378,28 +4396,28 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="6">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B114" s="7">
-        <v>45608.012511574178616103597724</v>
+        <v>45593.673831018623027681125076</v>
       </c>
       <c r="C114" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D114" s="9">
-        <v>45608.013055555660097586326112</v>
+        <v>45593.674166666771175830042592</v>
       </c>
       <c r="E114" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F114" s="11">
-        <v>45608</v>
+        <v>45590</v>
       </c>
       <c r="G114" s="12">
-        <v>10000</v>
+        <v>76400</v>
       </c>
       <c r="H114" t="s" s="13">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I114" t="s" s="14">
         <v>12</v>
@@ -4407,16 +4425,16 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="6">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B115" s="7">
-        <v>45708.64461805566032825254458</v>
+        <v>45708.645520833438106032391692</v>
       </c>
       <c r="C115" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D115" s="9">
-        <v>45708.6449652778825504755627</v>
+        <v>45708.652118055660328269735972</v>
       </c>
       <c r="E115" t="s" s="10">
         <v>10</v>
@@ -4425,10 +4443,10 @@
         <v>45708</v>
       </c>
       <c r="G115" s="12">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="H115" t="s" s="13">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I115" t="s" s="14">
         <v>12</v>
@@ -4436,28 +4454,28 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="6">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B116" s="7">
-        <v>45705.44166666677143202189664</v>
+        <v>45608.012511574178616103597724</v>
       </c>
       <c r="C116" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D116" s="9">
-        <v>45705.442719907512172765051604</v>
+        <v>45608.013055555660097586326112</v>
       </c>
       <c r="E116" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F116" s="11">
-        <v>45705</v>
+        <v>45608</v>
       </c>
       <c r="G116" s="12">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="H116" t="s" s="13">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I116" t="s" s="14">
         <v>12</v>
@@ -4465,28 +4483,28 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="6">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B117" s="7">
-        <v>45630.500185185289778760630464</v>
+        <v>45708.64461805566032825254458</v>
       </c>
       <c r="C117" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D117" s="9">
-        <v>45630.500729166771260243358852</v>
+        <v>45708.6449652778825504755627</v>
       </c>
       <c r="E117" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F117" s="11">
-        <v>45630</v>
+        <v>45708</v>
       </c>
       <c r="G117" s="12">
-        <v>25000</v>
+        <v>5000</v>
       </c>
       <c r="H117" t="s" s="13">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I117" t="s" s="14">
         <v>12</v>
@@ -4494,28 +4512,28 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="6">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B118" s="7">
-        <v>45663.492696759363928459664476</v>
+        <v>45705.44166666677143202189664</v>
       </c>
       <c r="C118" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D118" s="9">
-        <v>45663.49409722232689142583756</v>
+        <v>45705.442719907512172765051604</v>
       </c>
       <c r="E118" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F118" s="11">
-        <v>45646</v>
+        <v>45705</v>
       </c>
       <c r="G118" s="12">
-        <v>253800</v>
+        <v>16000</v>
       </c>
       <c r="H118" t="s" s="13">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I118" t="s" s="14">
         <v>12</v>
@@ -4523,28 +4541,28 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="6">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B119" s="7">
-        <v>45663.4950810186231877243889</v>
+        <v>45630.500185185289778760630464</v>
       </c>
       <c r="C119" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D119" s="9">
-        <v>45663.495393518623187725105208</v>
+        <v>45630.500729166771260243358852</v>
       </c>
       <c r="E119" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F119" s="11">
-        <v>45663</v>
+        <v>45630</v>
       </c>
       <c r="G119" s="12">
-        <v>1000</v>
+        <v>25000</v>
       </c>
       <c r="H119" t="s" s="13">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I119" t="s" s="14">
         <v>12</v>
@@ -4552,28 +4570,28 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="6">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B120" s="7">
-        <v>45694.701192129734370365698532</v>
+        <v>45663.492696759363928459664476</v>
       </c>
       <c r="C120" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D120" s="9">
-        <v>45694.705648148252888894431072</v>
+        <v>45663.49409722232689142583756</v>
       </c>
       <c r="E120" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F120" s="11">
-        <v>45694</v>
+        <v>45646</v>
       </c>
       <c r="G120" s="12">
-        <v>25000</v>
+        <v>253800</v>
       </c>
       <c r="H120" t="s" s="13">
-        <v>151</v>
+        <v>211</v>
       </c>
       <c r="I120" t="s" s="14">
         <v>12</v>
@@ -4581,28 +4599,28 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="6">
+        <v>212</v>
+      </c>
+      <c r="B121" s="7">
+        <v>45663.4950810186231877243889</v>
+      </c>
+      <c r="C121" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D121" s="9">
+        <v>45663.495393518623187725105208</v>
+      </c>
+      <c r="E121" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F121" s="11">
+        <v>45663</v>
+      </c>
+      <c r="G121" s="12">
+        <v>1000</v>
+      </c>
+      <c r="H121" t="s" s="13">
         <v>213</v>
-      </c>
-      <c r="B121" s="7">
-        <v>45663.50995370380837294366504</v>
-      </c>
-      <c r="C121" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D121" s="9">
-        <v>45663.510949074178743316316984</v>
-      </c>
-      <c r="E121" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F121" s="11">
-        <v>45653</v>
-      </c>
-      <c r="G121" s="12">
-        <v>20000</v>
-      </c>
-      <c r="H121" t="s" s="13">
-        <v>214</v>
       </c>
       <c r="I121" t="s" s="14">
         <v>12</v>
@@ -4610,28 +4628,28 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="6">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B122" s="7">
-        <v>45643.67586805566017933211138</v>
+        <v>45694.701192129734370365698532</v>
       </c>
       <c r="C122" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D122" s="9">
-        <v>45643.676296296400920073833728</v>
+        <v>45694.705648148252888894431072</v>
       </c>
       <c r="E122" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F122" s="11">
-        <v>45643</v>
+        <v>45694</v>
       </c>
       <c r="G122" s="12">
-        <v>2000</v>
+        <v>25000</v>
       </c>
       <c r="H122" t="s" s="13">
-        <v>92</v>
+        <v>153</v>
       </c>
       <c r="I122" t="s" s="14">
         <v>12</v>
@@ -4639,28 +4657,28 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="6">
+        <v>215</v>
+      </c>
+      <c r="B123" s="7">
+        <v>45663.50995370380837294366504</v>
+      </c>
+      <c r="C123" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D123" s="9">
+        <v>45663.510949074178743316316984</v>
+      </c>
+      <c r="E123" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F123" s="11">
+        <v>45653</v>
+      </c>
+      <c r="G123" s="12">
+        <v>20000</v>
+      </c>
+      <c r="H123" t="s" s="13">
         <v>216</v>
-      </c>
-      <c r="B123" s="7">
-        <v>45567.758356481585931241010488</v>
-      </c>
-      <c r="C123" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D123" s="9">
-        <v>45567.760497685289634949622228</v>
-      </c>
-      <c r="E123" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F123" s="11">
-        <v>45545</v>
-      </c>
-      <c r="G123" s="12">
-        <v>25000</v>
-      </c>
-      <c r="H123" t="s" s="13">
-        <v>151</v>
       </c>
       <c r="I123" t="s" s="14">
         <v>12</v>
@@ -4671,25 +4689,25 @@
         <v>217</v>
       </c>
       <c r="B124" s="7">
-        <v>45677.66932870380840539958052</v>
+        <v>45643.67586805566017933211138</v>
       </c>
       <c r="C124" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D124" s="9">
-        <v>45677.672719907512109111057492</v>
+        <v>45643.676296296400920073833728</v>
       </c>
       <c r="E124" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F124" s="11">
-        <v>45677</v>
+        <v>45643</v>
       </c>
       <c r="G124" s="12">
-        <v>3600</v>
+        <v>2000</v>
       </c>
       <c r="H124" t="s" s="13">
-        <v>218</v>
+        <v>93</v>
       </c>
       <c r="I124" t="s" s="14">
         <v>12</v>
@@ -4697,16 +4715,16 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="6">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B125" s="7">
-        <v>45593.689131944548953642123564</v>
+        <v>45567.758356481585931241010488</v>
       </c>
       <c r="C125" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D125" s="9">
-        <v>45593.690636574178583275202084</v>
+        <v>45567.760497685289634949622228</v>
       </c>
       <c r="E125" t="s" s="10">
         <v>10</v>
@@ -4715,10 +4733,10 @@
         <v>45545</v>
       </c>
       <c r="G125" s="12">
-        <v>12500</v>
+        <v>25000</v>
       </c>
       <c r="H125" t="s" s="13">
-        <v>220</v>
+        <v>153</v>
       </c>
       <c r="I125" t="s" s="14">
         <v>12</v>
@@ -4726,28 +4744,28 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="6">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B126" s="7">
-        <v>45628.696840277882367219621828</v>
+        <v>45677.66932870380840539958052</v>
       </c>
       <c r="C126" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D126" s="9">
-        <v>45628.711608796400885771992532</v>
+        <v>45677.672719907512109111057492</v>
       </c>
       <c r="E126" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F126" s="11">
-        <v>45628</v>
+        <v>45677</v>
       </c>
       <c r="G126" s="12">
-        <v>110000</v>
+        <v>3600</v>
       </c>
       <c r="H126" t="s" s="13">
-        <v>11</v>
+        <v>220</v>
       </c>
       <c r="I126" t="s" s="14">
         <v>12</v>
@@ -4755,28 +4773,28 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="6">
+        <v>221</v>
+      </c>
+      <c r="B127" s="7">
+        <v>45593.689131944548953642123564</v>
+      </c>
+      <c r="C127" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D127" s="9">
+        <v>45593.690636574178583275202084</v>
+      </c>
+      <c r="E127" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F127" s="11">
+        <v>45545</v>
+      </c>
+      <c r="G127" s="12">
+        <v>12500</v>
+      </c>
+      <c r="H127" t="s" s="13">
         <v>222</v>
-      </c>
-      <c r="B127" s="7">
-        <v>45673.707430555660248170026488</v>
-      </c>
-      <c r="C127" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D127" s="9">
-        <v>45673.708368055660248172175412</v>
-      </c>
-      <c r="E127" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F127" s="11">
-        <v>45673</v>
-      </c>
-      <c r="G127" s="12">
-        <v>7000</v>
-      </c>
-      <c r="H127" t="s" s="13">
-        <v>223</v>
       </c>
       <c r="I127" t="s" s="14">
         <v>12</v>
@@ -4784,25 +4802,25 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="6">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B128" s="7">
-        <v>45579.719756944548921621723348</v>
+        <v>45628.696840277882367219621828</v>
       </c>
       <c r="C128" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D128" s="9">
-        <v>45579.721041666771143846890392</v>
+        <v>45628.711608796400885771992532</v>
       </c>
       <c r="E128" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F128" s="11">
-        <v>45579</v>
+        <v>45628</v>
       </c>
       <c r="G128" s="12">
-        <v>43500</v>
+        <v>110000</v>
       </c>
       <c r="H128" t="s" s="13">
         <v>11</v>
@@ -4813,28 +4831,28 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="6">
+        <v>224</v>
+      </c>
+      <c r="B129" s="7">
+        <v>45673.707430555660248170026488</v>
+      </c>
+      <c r="C129" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D129" s="9">
+        <v>45673.708368055660248172175412</v>
+      </c>
+      <c r="E129" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F129" s="11">
+        <v>45673</v>
+      </c>
+      <c r="G129" s="12">
+        <v>7000</v>
+      </c>
+      <c r="H129" t="s" s="13">
         <v>225</v>
-      </c>
-      <c r="B129" s="7">
-        <v>45705.66313657417883993695418</v>
-      </c>
-      <c r="C129" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D129" s="9">
-        <v>45705.663761574178839938386796</v>
-      </c>
-      <c r="E129" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F129" s="11">
-        <v>45688</v>
-      </c>
-      <c r="G129" s="12">
-        <v>3500</v>
-      </c>
-      <c r="H129" t="s" s="13">
-        <v>135</v>
       </c>
       <c r="I129" t="s" s="14">
         <v>12</v>
@@ -4845,25 +4863,25 @@
         <v>226</v>
       </c>
       <c r="B130" s="7">
-        <v>45700.694861111215865585781744</v>
+        <v>45579.719756944548921621723348</v>
       </c>
       <c r="C130" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D130" s="9">
-        <v>45700.695046296401050771391408</v>
+        <v>45579.721041666771143846890392</v>
       </c>
       <c r="E130" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F130" s="11">
-        <v>45700</v>
+        <v>45579</v>
       </c>
       <c r="G130" s="12">
-        <v>14500</v>
+        <v>43500</v>
       </c>
       <c r="H130" t="s" s="13">
-        <v>103</v>
+        <v>11</v>
       </c>
       <c r="I130" t="s" s="14">
         <v>12</v>
@@ -4874,25 +4892,25 @@
         <v>227</v>
       </c>
       <c r="B131" s="7">
-        <v>45611.728344907511957954310716</v>
+        <v>45705.66313657417883993695418</v>
       </c>
       <c r="C131" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D131" s="9">
-        <v>45611.72870370380825425142944</v>
+        <v>45705.663761574178839938386796</v>
       </c>
       <c r="E131" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F131" s="11">
-        <v>45607</v>
+        <v>45688</v>
       </c>
       <c r="G131" s="12">
-        <v>2000</v>
+        <v>3500</v>
       </c>
       <c r="H131" t="s" s="13">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="I131" t="s" s="14">
         <v>12</v>
@@ -4903,25 +4921,25 @@
         <v>228</v>
       </c>
       <c r="B132" s="7">
-        <v>45645.708807870474998806801564</v>
+        <v>45700.694861111215865585781744</v>
       </c>
       <c r="C132" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D132" s="9">
-        <v>45645.709131944549072881618476</v>
+        <v>45700.695046296401050771391408</v>
       </c>
       <c r="E132" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F132" s="11">
-        <v>45645</v>
+        <v>45700</v>
       </c>
       <c r="G132" s="12">
-        <v>500</v>
+        <v>14500</v>
       </c>
       <c r="H132" t="s" s="13">
-        <v>229</v>
+        <v>104</v>
       </c>
       <c r="I132" t="s" s="14">
         <v>12</v>
@@ -4929,28 +4947,28 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="6">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B133" s="7">
-        <v>45672.70462962973431994549472</v>
+        <v>45611.728344907511957954310716</v>
       </c>
       <c r="C133" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D133" s="9">
-        <v>45672.70561342603061624404606</v>
+        <v>45611.72870370380825425142944</v>
       </c>
       <c r="E133" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F133" s="11">
-        <v>45672</v>
+        <v>45607</v>
       </c>
       <c r="G133" s="12">
-        <v>175000</v>
+        <v>2000</v>
       </c>
       <c r="H133" t="s" s="13">
-        <v>231</v>
+        <v>93</v>
       </c>
       <c r="I133" t="s" s="14">
         <v>12</v>
@@ -4958,28 +4976,28 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="6">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B134" s="7">
-        <v>45583.166238426030411003180052</v>
+        <v>45645.708807870474998806801564</v>
       </c>
       <c r="C134" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D134" s="9">
-        <v>45583.166527777882262855695152</v>
+        <v>45645.709131944549072881618476</v>
       </c>
       <c r="E134" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F134" s="11">
-        <v>45583</v>
+        <v>45645</v>
       </c>
       <c r="G134" s="12">
-        <v>100000</v>
+        <v>500</v>
       </c>
       <c r="H134" t="s" s="13">
-        <v>11</v>
+        <v>231</v>
       </c>
       <c r="I134" t="s" s="14">
         <v>12</v>
@@ -4987,28 +5005,28 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="6">
+        <v>232</v>
+      </c>
+      <c r="B135" s="7">
+        <v>45672.70462962973431994549472</v>
+      </c>
+      <c r="C135" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D135" s="9">
+        <v>45672.70561342603061624404606</v>
+      </c>
+      <c r="E135" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F135" s="11">
+        <v>45672</v>
+      </c>
+      <c r="G135" s="12">
+        <v>175000</v>
+      </c>
+      <c r="H135" t="s" s="13">
         <v>233</v>
-      </c>
-      <c r="B135" s="7">
-        <v>45630.498657407512000979350736</v>
-      </c>
-      <c r="C135" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D135" s="9">
-        <v>45630.49890046306755653546342</v>
-      </c>
-      <c r="E135" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F135" s="11">
-        <v>45630</v>
-      </c>
-      <c r="G135" s="12">
-        <v>13500</v>
-      </c>
-      <c r="H135" t="s" s="13">
-        <v>103</v>
       </c>
       <c r="I135" t="s" s="14">
         <v>12</v>
@@ -5019,25 +5037,25 @@
         <v>234</v>
       </c>
       <c r="B136" s="7">
-        <v>45707.673136574178844544247236</v>
+        <v>45583.166238426030411003180052</v>
       </c>
       <c r="C136" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D136" s="9">
-        <v>45707.6733217593640297298569</v>
+        <v>45583.166527777882262855695152</v>
       </c>
       <c r="E136" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F136" s="11">
-        <v>45707</v>
+        <v>45583</v>
       </c>
       <c r="G136" s="12">
-        <v>2500</v>
+        <v>100000</v>
       </c>
       <c r="H136" t="s" s="13">
-        <v>103</v>
+        <v>11</v>
       </c>
       <c r="I136" t="s" s="14">
         <v>12</v>
@@ -5048,25 +5066,25 @@
         <v>235</v>
       </c>
       <c r="B137" s="7">
-        <v>45567.918391203808153830061996</v>
+        <v>45713.641157407512191557391984</v>
       </c>
       <c r="C137" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D137" s="9">
-        <v>45567.929930555660005708364184</v>
+        <v>45713.641875000104784151629432</v>
       </c>
       <c r="E137" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F137" s="11">
-        <v>45567</v>
+        <v>45713</v>
       </c>
       <c r="G137" s="12">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="H137" t="s" s="13">
-        <v>236</v>
+        <v>104</v>
       </c>
       <c r="I137" t="s" s="14">
         <v>12</v>
@@ -5074,28 +5092,28 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="6">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B138" s="7">
-        <v>45670.717847222326907984013288</v>
+        <v>45630.498657407512000979350736</v>
       </c>
       <c r="C138" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D138" s="9">
-        <v>45670.718310185289870948037448</v>
+        <v>45630.49890046306755653546342</v>
       </c>
       <c r="E138" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F138" s="11">
-        <v>45670</v>
+        <v>45630</v>
       </c>
       <c r="G138" s="12">
-        <v>3000</v>
+        <v>13500</v>
       </c>
       <c r="H138" t="s" s="13">
-        <v>238</v>
+        <v>104</v>
       </c>
       <c r="I138" t="s" s="14">
         <v>12</v>
@@ -5103,28 +5121,28 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="6">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B139" s="7">
-        <v>45628.695324074178663512442704</v>
+        <v>45707.673136574178844544247236</v>
       </c>
       <c r="C139" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D139" s="9">
-        <v>45628.695810185289774624668072</v>
+        <v>45707.6733217593640297298569</v>
       </c>
       <c r="E139" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F139" s="11">
-        <v>45625</v>
+        <v>45707</v>
       </c>
       <c r="G139" s="12">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="H139" t="s" s="13">
-        <v>240</v>
+        <v>104</v>
       </c>
       <c r="I139" t="s" s="14">
         <v>12</v>
@@ -5132,28 +5150,28 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="6">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B140" s="7">
-        <v>45685.443854166771386183198796</v>
+        <v>45567.918391203808153830061996</v>
       </c>
       <c r="C140" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D140" s="9">
-        <v>45685.458321759363978808953796</v>
+        <v>45567.929930555660005708364184</v>
       </c>
       <c r="E140" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F140" s="11">
-        <v>45685</v>
+        <v>45567</v>
       </c>
       <c r="G140" s="12">
-        <v>2000</v>
+        <v>15000</v>
       </c>
       <c r="H140" t="s" s="13">
-        <v>25</v>
+        <v>239</v>
       </c>
       <c r="I140" t="s" s="14">
         <v>12</v>
@@ -5161,28 +5179,28 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="6">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B141" s="7">
-        <v>45629.627812500104591575805172</v>
+        <v>45670.717847222326907984013288</v>
       </c>
       <c r="C141" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D141" s="9">
-        <v>45629.628958333437924911764968</v>
+        <v>45670.718310185289870948037448</v>
       </c>
       <c r="E141" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F141" s="11">
-        <v>45629</v>
+        <v>45670</v>
       </c>
       <c r="G141" s="12">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="H141" t="s" s="13">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="I141" t="s" s="14">
         <v>12</v>
@@ -5190,28 +5208,28 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="6">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B142" s="7">
-        <v>45607.620902777882318909661384</v>
+        <v>45628.695324074178663512442704</v>
       </c>
       <c r="C142" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D142" s="9">
-        <v>45607.621203703808244836277088</v>
+        <v>45628.695810185289774624668072</v>
       </c>
       <c r="E142" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F142" s="11">
-        <v>45607</v>
+        <v>45625</v>
       </c>
       <c r="G142" s="12">
         <v>2000</v>
       </c>
       <c r="H142" t="s" s="13">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="I142" t="s" s="14">
         <v>12</v>
@@ -5222,25 +5240,25 @@
         <v>244</v>
       </c>
       <c r="B143" s="7">
-        <v>45607.620266203808244834128164</v>
+        <v>45685.443854166771386183198796</v>
       </c>
       <c r="C143" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D143" s="9">
-        <v>45607.62071759269713372405172</v>
+        <v>45685.458321759363978808953796</v>
       </c>
       <c r="E143" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F143" s="11">
-        <v>45607</v>
+        <v>45685</v>
       </c>
       <c r="G143" s="12">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="H143" t="s" s="13">
-        <v>245</v>
+        <v>25</v>
       </c>
       <c r="I143" t="s" s="14">
         <v>12</v>
@@ -5248,28 +5266,28 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="6">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B144" s="7">
-        <v>45611.725590277882328318366964</v>
+        <v>45629.627812500104591575805172</v>
       </c>
       <c r="C144" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D144" s="9">
-        <v>45611.726412037141587579509848</v>
+        <v>45629.628958333437924911764968</v>
       </c>
       <c r="E144" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F144" s="11">
-        <v>45611</v>
+        <v>45629</v>
       </c>
       <c r="G144" s="12">
-        <v>30000</v>
+        <v>5000</v>
       </c>
       <c r="H144" t="s" s="13">
-        <v>247</v>
+        <v>182</v>
       </c>
       <c r="I144" t="s" s="14">
         <v>12</v>
@@ -5277,28 +5295,28 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="6">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B145" s="7">
-        <v>45681.703136574178785016187204</v>
+        <v>45607.620902777882318909661384</v>
       </c>
       <c r="C145" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D145" s="9">
-        <v>45681.705011574178785020485052</v>
+        <v>45607.621203703808244836277088</v>
       </c>
       <c r="E145" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F145" s="11">
-        <v>45681</v>
+        <v>45607</v>
       </c>
       <c r="G145" s="12">
-        <v>50000</v>
+        <v>2000</v>
       </c>
       <c r="H145" t="s" s="13">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="I145" t="s" s="14">
         <v>12</v>
@@ -5306,28 +5324,28 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="6">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B146" s="7">
-        <v>45622.689606481586057153630728</v>
+        <v>45607.620266203808244834128164</v>
       </c>
       <c r="C146" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D146" s="9">
-        <v>45622.6898148149193904874416</v>
+        <v>45607.62071759269713372405172</v>
       </c>
       <c r="E146" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F146" s="11">
-        <v>45622</v>
+        <v>45607</v>
       </c>
       <c r="G146" s="12">
-        <v>13000</v>
+        <v>10000</v>
       </c>
       <c r="H146" t="s" s="13">
-        <v>103</v>
+        <v>248</v>
       </c>
       <c r="I146" t="s" s="14">
         <v>12</v>
@@ -5335,28 +5353,28 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="6">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B147" s="7">
-        <v>45642.442500000104620949447328</v>
+        <v>45611.725590277882328318366964</v>
       </c>
       <c r="C147" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D147" s="9">
-        <v>45642.442719907512028357358804</v>
+        <v>45611.726412037141587579509848</v>
       </c>
       <c r="E147" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F147" s="11">
-        <v>45642</v>
+        <v>45611</v>
       </c>
       <c r="G147" s="12">
-        <v>12500</v>
+        <v>30000</v>
       </c>
       <c r="H147" t="s" s="13">
-        <v>103</v>
+        <v>250</v>
       </c>
       <c r="I147" t="s" s="14">
         <v>12</v>
@@ -5364,28 +5382,28 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="6">
+        <v>251</v>
+      </c>
+      <c r="B148" s="7">
+        <v>45681.703136574178785016187204</v>
+      </c>
+      <c r="C148" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D148" s="9">
+        <v>45681.705011574178785020485052</v>
+      </c>
+      <c r="E148" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F148" s="11">
+        <v>45681</v>
+      </c>
+      <c r="G148" s="12">
+        <v>50000</v>
+      </c>
+      <c r="H148" t="s" s="13">
         <v>252</v>
-      </c>
-      <c r="B148" s="7">
-        <v>45699.700937500104752196413244</v>
-      </c>
-      <c r="C148" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D148" s="9">
-        <v>45699.70115740751215960432472</v>
-      </c>
-      <c r="E148" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F148" s="11">
-        <v>45699</v>
-      </c>
-      <c r="G148" s="12">
-        <v>7500</v>
-      </c>
-      <c r="H148" t="s" s="13">
-        <v>70</v>
       </c>
       <c r="I148" t="s" s="14">
         <v>12</v>
@@ -5396,22 +5414,22 @@
         <v>253</v>
       </c>
       <c r="B149" s="7">
-        <v>45699.703055555660307756823776</v>
+        <v>45715.649444444549233197795648</v>
       </c>
       <c r="C149" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D149" s="9">
-        <v>45699.704236111215863315085384</v>
+        <v>45715.64994212973441838412162</v>
       </c>
       <c r="E149" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F149" s="11">
-        <v>45673</v>
+        <v>45715</v>
       </c>
       <c r="G149" s="12">
-        <v>1000</v>
+        <v>25000</v>
       </c>
       <c r="H149" t="s" s="13">
         <v>254</v>
@@ -5425,25 +5443,25 @@
         <v>255</v>
       </c>
       <c r="B150" s="7">
-        <v>45636.678726851956459589661368</v>
+        <v>45622.689606481586057153630728</v>
       </c>
       <c r="C150" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D150" s="9">
-        <v>45636.679131944549052183182508</v>
+        <v>45622.6898148149193904874416</v>
       </c>
       <c r="E150" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F150" s="11">
-        <v>45636</v>
+        <v>45622</v>
       </c>
       <c r="G150" s="12">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="H150" t="s" s="13">
-        <v>240</v>
+        <v>104</v>
       </c>
       <c r="I150" t="s" s="14">
         <v>12</v>
@@ -5454,25 +5472,25 @@
         <v>256</v>
       </c>
       <c r="B151" s="7">
-        <v>45552.782418981585896913382204</v>
+        <v>45642.442500000104620949447328</v>
       </c>
       <c r="C151" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D151" s="9">
-        <v>45552.783472222326637656537168</v>
+        <v>45642.442719907512028357358804</v>
       </c>
       <c r="E151" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F151" s="11">
-        <v>45552</v>
+        <v>45642</v>
       </c>
       <c r="G151" s="12">
-        <v>20000</v>
+        <v>12500</v>
       </c>
       <c r="H151" t="s" s="13">
-        <v>257</v>
+        <v>104</v>
       </c>
       <c r="I151" t="s" s="14">
         <v>12</v>
@@ -5480,28 +5498,28 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="6">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B152" s="7">
-        <v>45677.660462963067664638517856</v>
+        <v>45699.700937500104752196413244</v>
       </c>
       <c r="C152" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D152" s="9">
-        <v>45677.660868055660257232038996</v>
+        <v>45699.70115740751215960432472</v>
       </c>
       <c r="E152" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F152" s="11">
-        <v>45677</v>
+        <v>45699</v>
       </c>
       <c r="G152" s="12">
-        <v>2000</v>
+        <v>7500</v>
       </c>
       <c r="H152" t="s" s="13">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="I152" t="s" s="14">
         <v>12</v>
@@ -5509,28 +5527,28 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="6">
+        <v>258</v>
+      </c>
+      <c r="B153" s="7">
+        <v>45699.703055555660307756823776</v>
+      </c>
+      <c r="C153" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D153" s="9">
+        <v>45699.704236111215863315085384</v>
+      </c>
+      <c r="E153" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F153" s="11">
+        <v>45673</v>
+      </c>
+      <c r="G153" s="12">
+        <v>1000</v>
+      </c>
+      <c r="H153" t="s" s="13">
         <v>259</v>
-      </c>
-      <c r="B153" s="7">
-        <v>45628.694594907511996844104652</v>
-      </c>
-      <c r="C153" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D153" s="9">
-        <v>45628.695150463067552400933644</v>
-      </c>
-      <c r="E153" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F153" s="11">
-        <v>45625</v>
-      </c>
-      <c r="G153" s="12">
-        <v>2000</v>
-      </c>
-      <c r="H153" t="s" s="13">
-        <v>46</v>
       </c>
       <c r="I153" t="s" s="14">
         <v>12</v>
@@ -5541,25 +5559,25 @@
         <v>260</v>
       </c>
       <c r="B154" s="7">
-        <v>45677.656238426030627591797396</v>
+        <v>45636.678726851956459589661368</v>
       </c>
       <c r="C154" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D154" s="9">
-        <v>45677.65949074084544241406712</v>
+        <v>45636.679131944549052183182508</v>
       </c>
       <c r="E154" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F154" s="11">
-        <v>45677</v>
+        <v>45636</v>
       </c>
       <c r="G154" s="12">
-        <v>110000</v>
+        <v>2000</v>
       </c>
       <c r="H154" t="s" s="13">
-        <v>11</v>
+        <v>243</v>
       </c>
       <c r="I154" t="s" s="14">
         <v>12</v>
@@ -5570,25 +5588,25 @@
         <v>261</v>
       </c>
       <c r="B155" s="7">
-        <v>45593.666157407511916552424624</v>
+        <v>45552.782418981585896913382204</v>
       </c>
       <c r="C155" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D155" s="9">
-        <v>45593.667638888993398037301936</v>
+        <v>45552.783472222326637656537168</v>
       </c>
       <c r="E155" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F155" s="11">
-        <v>45593</v>
+        <v>45552</v>
       </c>
       <c r="G155" s="12">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="H155" t="s" s="13">
-        <v>203</v>
+        <v>262</v>
       </c>
       <c r="I155" t="s" s="14">
         <v>12</v>
@@ -5596,28 +5614,28 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="6">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B156" s="7">
-        <v>45700.686736111215865567157736</v>
+        <v>45677.660462963067664638517856</v>
       </c>
       <c r="C156" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D156" s="9">
-        <v>45700.690416666771421131149808</v>
+        <v>45677.660868055660257232038996</v>
       </c>
       <c r="E156" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F156" s="11">
-        <v>45700</v>
+        <v>45677</v>
       </c>
       <c r="G156" s="12">
-        <v>27000</v>
+        <v>2000</v>
       </c>
       <c r="H156" t="s" s="13">
-        <v>263</v>
+        <v>121</v>
       </c>
       <c r="I156" t="s" s="14">
         <v>12</v>
@@ -5628,25 +5646,25 @@
         <v>264</v>
       </c>
       <c r="B157" s="7">
-        <v>45572.757719907511868626405268</v>
+        <v>45628.694594907511996844104652</v>
       </c>
       <c r="C157" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D157" s="9">
-        <v>45572.75804398158594270122218</v>
+        <v>45628.695150463067552400933644</v>
       </c>
       <c r="E157" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F157" s="11">
-        <v>45572</v>
+        <v>45625</v>
       </c>
       <c r="G157" s="12">
-        <v>29000</v>
+        <v>2000</v>
       </c>
       <c r="H157" t="s" s="13">
-        <v>265</v>
+        <v>46</v>
       </c>
       <c r="I157" t="s" s="14">
         <v>12</v>
@@ -5654,28 +5672,28 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="6">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B158" s="7">
-        <v>45692.681863426030662033318652</v>
+        <v>45677.656238426030627591797396</v>
       </c>
       <c r="C158" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D158" s="9">
-        <v>45692.682337963067699071443416</v>
+        <v>45677.65949074084544241406712</v>
       </c>
       <c r="E158" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F158" s="11">
-        <v>45692</v>
+        <v>45677</v>
       </c>
       <c r="G158" s="12">
-        <v>7000</v>
+        <v>110000</v>
       </c>
       <c r="H158" t="s" s="13">
-        <v>223</v>
+        <v>11</v>
       </c>
       <c r="I158" t="s" s="14">
         <v>12</v>
@@ -5683,28 +5701,28 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="6">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B159" s="7">
-        <v>45698.718020833438083276719148</v>
+        <v>45593.666157407511916552424624</v>
       </c>
       <c r="C159" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D159" s="9">
-        <v>45698.71869212973437957455418</v>
+        <v>45593.667638888993398037301936</v>
       </c>
       <c r="E159" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F159" s="11">
-        <v>45698</v>
+        <v>45593</v>
       </c>
       <c r="G159" s="12">
-        <v>26250</v>
+        <v>5000</v>
       </c>
       <c r="H159" t="s" s="13">
-        <v>268</v>
+        <v>205</v>
       </c>
       <c r="I159" t="s" s="14">
         <v>12</v>
@@ -5712,28 +5730,28 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="6">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B160" s="7">
-        <v>45663.491099537141706233781124</v>
+        <v>45700.686736111215865567157736</v>
       </c>
       <c r="C160" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D160" s="9">
-        <v>45663.492476851956521051753</v>
+        <v>45700.690416666771421131149808</v>
       </c>
       <c r="E160" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F160" s="11">
-        <v>45663</v>
+        <v>45700</v>
       </c>
       <c r="G160" s="12">
-        <v>125000</v>
+        <v>27000</v>
       </c>
       <c r="H160" t="s" s="13">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="I160" t="s" s="14">
         <v>12</v>
@@ -5741,28 +5759,28 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="6">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B161" s="7">
-        <v>45572.727013888993350037502856</v>
+        <v>45572.757719907511868626405268</v>
       </c>
       <c r="C161" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D161" s="9">
-        <v>45572.727442129734090779225204</v>
+        <v>45572.75804398158594270122218</v>
       </c>
       <c r="E161" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F161" s="11">
-        <v>45553</v>
+        <v>45572</v>
       </c>
       <c r="G161" s="12">
-        <v>66000</v>
+        <v>29000</v>
       </c>
       <c r="H161" t="s" s="13">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I161" t="s" s="14">
         <v>12</v>
@@ -5770,28 +5788,28 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="6">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B162" s="7">
-        <v>45700.697314814919569295109792</v>
+        <v>45692.681863426030662033318652</v>
       </c>
       <c r="C162" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D162" s="9">
-        <v>45700.698009259364013741146032</v>
+        <v>45692.682337963067699071443416</v>
       </c>
       <c r="E162" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F162" s="11">
-        <v>45700</v>
+        <v>45692</v>
       </c>
       <c r="G162" s="12">
-        <v>2500</v>
+        <v>7000</v>
       </c>
       <c r="H162" t="s" s="13">
-        <v>274</v>
+        <v>225</v>
       </c>
       <c r="I162" t="s" s="14">
         <v>12</v>
@@ -5799,28 +5817,28 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="6">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B163" s="7">
-        <v>45594.726006944548956018833508</v>
+        <v>45698.718020833438083276719148</v>
       </c>
       <c r="C163" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D163" s="9">
-        <v>45594.7265625001045115756625</v>
+        <v>45698.71869212973437957455418</v>
       </c>
       <c r="E163" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F163" s="11">
-        <v>45594</v>
+        <v>45698</v>
       </c>
       <c r="G163" s="12">
-        <v>5000</v>
+        <v>26250</v>
       </c>
       <c r="H163" t="s" s="13">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="I163" t="s" s="14">
         <v>12</v>
@@ -5828,28 +5846,28 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="6">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B164" s="7">
-        <v>45685.458599537141756587368292</v>
+        <v>45663.491099537141706233781124</v>
       </c>
       <c r="C164" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D164" s="9">
-        <v>45685.458900463067682513983996</v>
+        <v>45663.492476851956521051753</v>
       </c>
       <c r="E164" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F164" s="11">
-        <v>45685</v>
+        <v>45663</v>
       </c>
       <c r="G164" s="12">
-        <v>25000</v>
+        <v>125000</v>
       </c>
       <c r="H164" t="s" s="13">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I164" t="s" s="14">
         <v>12</v>
@@ -5857,28 +5875,28 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="6">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B165" s="7">
-        <v>45674.116620370475063922780304</v>
+        <v>45572.727013888993350037502856</v>
       </c>
       <c r="C165" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D165" s="9">
-        <v>45674.116909722326915775295404</v>
+        <v>45572.727442129734090779225204</v>
       </c>
       <c r="E165" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F165" s="11">
-        <v>45674</v>
+        <v>45553</v>
       </c>
       <c r="G165" s="12">
-        <v>2000</v>
+        <v>66000</v>
       </c>
       <c r="H165" t="s" s="13">
-        <v>56</v>
+        <v>277</v>
       </c>
       <c r="I165" t="s" s="14">
         <v>12</v>
@@ -5886,28 +5904,28 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="6">
+        <v>278</v>
+      </c>
+      <c r="B166" s="7">
+        <v>45700.697314814919569295109792</v>
+      </c>
+      <c r="C166" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D166" s="9">
+        <v>45700.698009259364013741146032</v>
+      </c>
+      <c r="E166" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F166" s="11">
+        <v>45700</v>
+      </c>
+      <c r="G166" s="12">
+        <v>2500</v>
+      </c>
+      <c r="H166" t="s" s="13">
         <v>279</v>
-      </c>
-      <c r="B166" s="7">
-        <v>45681.705347222326933169402568</v>
-      </c>
-      <c r="C166" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D166" s="9">
-        <v>45681.706701388993599839173236</v>
-      </c>
-      <c r="E166" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F166" s="11">
-        <v>45681</v>
-      </c>
-      <c r="G166" s="12">
-        <v>11000</v>
-      </c>
-      <c r="H166" t="s" s="13">
-        <v>280</v>
       </c>
       <c r="I166" t="s" s="14">
         <v>12</v>
@@ -5915,28 +5933,28 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="6">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B167" s="7">
-        <v>45611.415763888993438719298488</v>
+        <v>45594.726006944548956018833508</v>
       </c>
       <c r="C167" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D167" s="9">
-        <v>45611.422037037141586881825856</v>
+        <v>45594.7265625001045115756625</v>
       </c>
       <c r="E167" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F167" s="11">
-        <v>45611</v>
+        <v>45594</v>
       </c>
       <c r="G167" s="12">
-        <v>100000</v>
+        <v>5000</v>
       </c>
       <c r="H167" t="s" s="13">
-        <v>282</v>
+        <v>254</v>
       </c>
       <c r="I167" t="s" s="14">
         <v>12</v>
@@ -5944,28 +5962,28 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="6">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B168" s="7">
-        <v>45707.673692129734400101076228</v>
+        <v>45685.458599537141756587368292</v>
       </c>
       <c r="C168" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D168" s="9">
-        <v>45707.673865740845511212585288</v>
+        <v>45685.458900463067682513983996</v>
       </c>
       <c r="E168" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F168" s="11">
-        <v>45707</v>
+        <v>45685</v>
       </c>
       <c r="G168" s="12">
-        <v>1000</v>
+        <v>25000</v>
       </c>
       <c r="H168" t="s" s="13">
-        <v>25</v>
+        <v>254</v>
       </c>
       <c r="I168" t="s" s="14">
         <v>12</v>
@@ -5973,28 +5991,28 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="6">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B169" s="7">
-        <v>45567.930659722326672376702236</v>
+        <v>45674.116620370475063922780304</v>
       </c>
       <c r="C169" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D169" s="9">
-        <v>45567.93090277788222793281492</v>
+        <v>45674.116909722326915775295404</v>
       </c>
       <c r="E169" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F169" s="11">
-        <v>45567</v>
+        <v>45674</v>
       </c>
       <c r="G169" s="12">
-        <v>7000</v>
+        <v>2000</v>
       </c>
       <c r="H169" t="s" s="13">
-        <v>223</v>
+        <v>56</v>
       </c>
       <c r="I169" t="s" s="14">
         <v>12</v>
@@ -6002,28 +6020,28 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="6">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B170" s="7">
-        <v>45630.499085648252741721073084</v>
+        <v>45681.705347222326933169402568</v>
       </c>
       <c r="C170" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D170" s="9">
-        <v>45630.499317129734223203085164</v>
+        <v>45681.706701388993599839173236</v>
       </c>
       <c r="E170" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F170" s="11">
-        <v>45630</v>
+        <v>45681</v>
       </c>
       <c r="G170" s="12">
-        <v>1000</v>
+        <v>11000</v>
       </c>
       <c r="H170" t="s" s="13">
-        <v>25</v>
+        <v>284</v>
       </c>
       <c r="I170" t="s" s="14">
         <v>12</v>
@@ -6031,28 +6049,28 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="6">
+        <v>285</v>
+      </c>
+      <c r="B171" s="7">
+        <v>45611.415763888993438719298488</v>
+      </c>
+      <c r="C171" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D171" s="9">
+        <v>45611.422037037141586881825856</v>
+      </c>
+      <c r="E171" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F171" s="11">
+        <v>45611</v>
+      </c>
+      <c r="G171" s="12">
+        <v>100000</v>
+      </c>
+      <c r="H171" t="s" s="13">
         <v>286</v>
-      </c>
-      <c r="B171" s="7">
-        <v>45643.673738426030549697600244</v>
-      </c>
-      <c r="C171" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D171" s="9">
-        <v>45643.675567129734253405495676</v>
-      </c>
-      <c r="E171" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F171" s="11">
-        <v>45643</v>
-      </c>
-      <c r="G171" s="12">
-        <v>15000</v>
-      </c>
-      <c r="H171" t="s" s="13">
-        <v>287</v>
       </c>
       <c r="I171" t="s" s="14">
         <v>12</v>
@@ -6060,28 +6078,28 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="6">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B172" s="7">
-        <v>45685.462650463067682522579692</v>
+        <v>45707.673692129734400101076228</v>
       </c>
       <c r="C172" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D172" s="9">
-        <v>45685.46377314825286771033828</v>
+        <v>45707.673865740845511212585288</v>
       </c>
       <c r="E172" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F172" s="11">
-        <v>45685</v>
+        <v>45707</v>
       </c>
       <c r="G172" s="12">
-        <v>8000</v>
+        <v>1000</v>
       </c>
       <c r="H172" t="s" s="13">
-        <v>289</v>
+        <v>25</v>
       </c>
       <c r="I172" t="s" s="14">
         <v>12</v>
@@ -6089,28 +6107,28 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="6">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B173" s="7">
-        <v>45678.386990740845444081632144</v>
+        <v>45567.930659722326672376702236</v>
       </c>
       <c r="C173" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D173" s="9">
-        <v>45678.387349537141740378750868</v>
+        <v>45567.93090277788222793281492</v>
       </c>
       <c r="E173" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F173" s="11">
-        <v>45678</v>
+        <v>45567</v>
       </c>
       <c r="G173" s="12">
-        <v>2000</v>
+        <v>7000</v>
       </c>
       <c r="H173" t="s" s="13">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="I173" t="s" s="14">
         <v>12</v>
@@ -6118,28 +6136,28 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="6">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B174" s="7">
-        <v>45700.682152777882532223318552</v>
+        <v>45630.499085648252741721073084</v>
       </c>
       <c r="C174" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D174" s="9">
-        <v>45700.685694444549198898103376</v>
+        <v>45630.499317129734223203085164</v>
       </c>
       <c r="E174" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F174" s="11">
-        <v>45700</v>
+        <v>45630</v>
       </c>
       <c r="G174" s="12">
-        <v>200900</v>
+        <v>1000</v>
       </c>
       <c r="H174" t="s" s="13">
-        <v>292</v>
+        <v>25</v>
       </c>
       <c r="I174" t="s" s="14">
         <v>12</v>
@@ -6147,28 +6165,28 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="6">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B175" s="7">
-        <v>45670.71359953714172278909162</v>
+        <v>45643.673738426030549697600244</v>
       </c>
       <c r="C175" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D175" s="9">
-        <v>45670.714027777882463530813968</v>
+        <v>45643.675567129734253405495676</v>
       </c>
       <c r="E175" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F175" s="11">
-        <v>45670</v>
+        <v>45643</v>
       </c>
       <c r="G175" s="12">
-        <v>110000</v>
+        <v>15000</v>
       </c>
       <c r="H175" t="s" s="13">
-        <v>11</v>
+        <v>291</v>
       </c>
       <c r="I175" t="s" s="14">
         <v>12</v>
@@ -6176,28 +6194,28 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="6">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B176" s="7">
-        <v>45576.793391203808174173209196</v>
+        <v>45685.462650463067682522579692</v>
       </c>
       <c r="C176" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D176" s="9">
-        <v>45579.69832175936373638740474</v>
+        <v>45685.46377314825286771033828</v>
       </c>
       <c r="E176" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F176" s="11">
-        <v>45575</v>
+        <v>45685</v>
       </c>
       <c r="G176" s="12">
-        <v>1500</v>
+        <v>8000</v>
       </c>
       <c r="H176" t="s" s="13">
-        <v>139</v>
+        <v>293</v>
       </c>
       <c r="I176" t="s" s="14">
         <v>12</v>
@@ -6205,28 +6223,28 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="6">
+        <v>294</v>
+      </c>
+      <c r="B177" s="7">
+        <v>45715.366921296401084402052008</v>
+      </c>
+      <c r="C177" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D177" s="9">
+        <v>45715.367546296401084403484624</v>
+      </c>
+      <c r="E177" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F177" s="11">
+        <v>45714</v>
+      </c>
+      <c r="G177" s="12">
+        <v>14000</v>
+      </c>
+      <c r="H177" t="s" s="13">
         <v>295</v>
-      </c>
-      <c r="B177" s="7">
-        <v>45618.458055555660121528204704</v>
-      </c>
-      <c r="C177" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D177" s="9">
-        <v>45618.458379629734195603021616</v>
-      </c>
-      <c r="E177" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F177" s="11">
-        <v>45617</v>
-      </c>
-      <c r="G177" s="12">
-        <v>1000</v>
-      </c>
-      <c r="H177" t="s" s="13">
-        <v>122</v>
       </c>
       <c r="I177" t="s" s="14">
         <v>12</v>
@@ -6237,25 +6255,25 @@
         <v>296</v>
       </c>
       <c r="B178" s="7">
-        <v>45593.658067129734138756102428</v>
+        <v>45678.386990740845444081632144</v>
       </c>
       <c r="C178" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D178" s="9">
-        <v>45593.658379629734138756818736</v>
+        <v>45678.387349537141740378750868</v>
       </c>
       <c r="E178" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F178" s="11">
-        <v>45588</v>
+        <v>45678</v>
       </c>
       <c r="G178" s="12">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H178" t="s" s="13">
-        <v>25</v>
+        <v>243</v>
       </c>
       <c r="I178" t="s" s="14">
         <v>12</v>
@@ -6266,22 +6284,22 @@
         <v>297</v>
       </c>
       <c r="B179" s="7">
-        <v>45644.5885416667712925352398</v>
+        <v>45700.682152777882532223318552</v>
       </c>
       <c r="C179" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D179" s="9">
-        <v>45644.588981481586107351062752</v>
+        <v>45700.685694444549198898103376</v>
       </c>
       <c r="E179" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F179" s="11">
-        <v>45644</v>
+        <v>45700</v>
       </c>
       <c r="G179" s="12">
-        <v>1000</v>
+        <v>200900</v>
       </c>
       <c r="H179" t="s" s="13">
         <v>298</v>
@@ -6295,25 +6313,25 @@
         <v>299</v>
       </c>
       <c r="B180" s="7">
-        <v>45700.701006944549198933202468</v>
+        <v>45670.71359953714172278909162</v>
       </c>
       <c r="C180" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D180" s="9">
-        <v>45700.70347222232697671663112</v>
+        <v>45670.714027777882463530813968</v>
       </c>
       <c r="E180" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F180" s="11">
-        <v>45700</v>
+        <v>45670</v>
       </c>
       <c r="G180" s="12">
-        <v>3500</v>
+        <v>110000</v>
       </c>
       <c r="H180" t="s" s="13">
-        <v>300</v>
+        <v>11</v>
       </c>
       <c r="I180" t="s" s="14">
         <v>12</v>
@@ -6321,28 +6339,28 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="6">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B181" s="7">
-        <v>45663.511215277882447020630876</v>
+        <v>45576.793391203808174173209196</v>
       </c>
       <c r="C181" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D181" s="9">
-        <v>45663.511724537141706281057452</v>
+        <v>45579.69832175936373638740474</v>
       </c>
       <c r="E181" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F181" s="11">
-        <v>45663</v>
+        <v>45575</v>
       </c>
       <c r="G181" s="12">
-        <v>25000</v>
+        <v>1500</v>
       </c>
       <c r="H181" t="s" s="13">
-        <v>276</v>
+        <v>141</v>
       </c>
       <c r="I181" t="s" s="14">
         <v>12</v>
@@ -6350,28 +6368,28 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="6">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B182" s="7">
-        <v>45567.742372685289634908076364</v>
+        <v>45618.458055555660121528204704</v>
       </c>
       <c r="C182" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D182" s="9">
-        <v>45567.742581018622968241887236</v>
+        <v>45618.458379629734195603021616</v>
       </c>
       <c r="E182" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F182" s="11">
-        <v>45567</v>
+        <v>45617</v>
       </c>
       <c r="G182" s="12">
-        <v>20000</v>
+        <v>1000</v>
       </c>
       <c r="H182" t="s" s="13">
-        <v>303</v>
+        <v>123</v>
       </c>
       <c r="I182" t="s" s="14">
         <v>12</v>
@@ -6379,28 +6397,28 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="6">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B183" s="7">
-        <v>45618.716504629734196194692024</v>
+        <v>45593.658067129734138756102428</v>
       </c>
       <c r="C183" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D183" s="9">
-        <v>45618.71718750010456656662766</v>
+        <v>45593.658379629734138756818736</v>
       </c>
       <c r="E183" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F183" s="11">
-        <v>45618</v>
+        <v>45588</v>
       </c>
       <c r="G183" s="12">
-        <v>25000</v>
+        <v>1000</v>
       </c>
       <c r="H183" t="s" s="13">
-        <v>305</v>
+        <v>25</v>
       </c>
       <c r="I183" t="s" s="14">
         <v>12</v>
@@ -6408,28 +6426,28 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="6">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B184" s="7">
-        <v>45579.7167245371415142073651</v>
+        <v>45644.5885416667712925352398</v>
       </c>
       <c r="C184" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D184" s="9">
-        <v>45579.7170138889933660598802</v>
+        <v>45644.588981481586107351062752</v>
       </c>
       <c r="E184" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F184" s="11">
-        <v>45579</v>
+        <v>45644</v>
       </c>
       <c r="G184" s="12">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="H184" t="s" s="13">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="I184" t="s" s="14">
         <v>12</v>
@@ -6437,28 +6455,28 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="6">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B185" s="7">
-        <v>45600.4988425926971173993924</v>
+        <v>45700.701006944549198933202468</v>
       </c>
       <c r="C185" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D185" s="9">
-        <v>45600.499178240845265548309916</v>
+        <v>45700.70347222232697671663112</v>
       </c>
       <c r="E185" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F185" s="11">
-        <v>45600</v>
+        <v>45700</v>
       </c>
       <c r="G185" s="12">
-        <v>1000</v>
+        <v>3500</v>
       </c>
       <c r="H185" t="s" s="13">
-        <v>56</v>
+        <v>306</v>
       </c>
       <c r="I185" t="s" s="14">
         <v>12</v>
@@ -6466,28 +6484,28 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="6">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B186" s="7">
-        <v>45629.6273148149194063894792</v>
+        <v>45663.511215277882447020630876</v>
       </c>
       <c r="C186" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D186" s="9">
-        <v>45629.62754629640088787149128</v>
+        <v>45663.511724537141706281057452</v>
       </c>
       <c r="E186" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F186" s="11">
-        <v>45629</v>
+        <v>45663</v>
       </c>
       <c r="G186" s="12">
-        <v>1000</v>
+        <v>25000</v>
       </c>
       <c r="H186" t="s" s="13">
-        <v>25</v>
+        <v>254</v>
       </c>
       <c r="I186" t="s" s="14">
         <v>12</v>
@@ -6495,28 +6513,28 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="6">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B187" s="7">
-        <v>45705.640381944549210255166716</v>
+        <v>45567.742372685289634908076364</v>
       </c>
       <c r="C187" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D187" s="9">
-        <v>45705.64103009269735840480054</v>
+        <v>45567.742581018622968241887236</v>
       </c>
       <c r="E187" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F187" s="11">
-        <v>45705</v>
+        <v>45567</v>
       </c>
       <c r="G187" s="12">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="H187" t="s" s="13">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="I187" t="s" s="14">
         <v>12</v>
@@ -6524,28 +6542,28 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="6">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B188" s="7">
-        <v>45677.66111111121581278815168</v>
+        <v>45618.716504629734196194692024</v>
       </c>
       <c r="C188" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D188" s="9">
-        <v>45677.661446759363960937069196</v>
+        <v>45618.71718750010456656662766</v>
       </c>
       <c r="E188" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F188" s="11">
-        <v>45677</v>
+        <v>45618</v>
       </c>
       <c r="G188" s="12">
-        <v>4000</v>
+        <v>25000</v>
       </c>
       <c r="H188" t="s" s="13">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="I188" t="s" s="14">
         <v>12</v>
@@ -6553,28 +6571,28 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="6">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B189" s="7">
-        <v>45673.74583333343802603583056</v>
+        <v>45579.7167245371415142073651</v>
       </c>
       <c r="C189" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D189" s="9">
-        <v>45673.746030092697285295540828</v>
+        <v>45579.7170138889933660598802</v>
       </c>
       <c r="E189" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F189" s="11">
-        <v>45673</v>
+        <v>45579</v>
       </c>
       <c r="G189" s="12">
-        <v>13000</v>
+        <v>2500</v>
       </c>
       <c r="H189" t="s" s="13">
-        <v>103</v>
+        <v>313</v>
       </c>
       <c r="I189" t="s" s="14">
         <v>12</v>
@@ -6582,28 +6600,28 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="6">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B190" s="7">
-        <v>45602.219710648252676899496932</v>
+        <v>45600.4988425926971173993924</v>
       </c>
       <c r="C190" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D190" s="9">
-        <v>45602.223738426030454686507124</v>
+        <v>45600.499178240845265548309916</v>
       </c>
       <c r="E190" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F190" s="11">
-        <v>45602</v>
+        <v>45600</v>
       </c>
       <c r="G190" s="12">
         <v>1000</v>
       </c>
       <c r="H190" t="s" s="13">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="I190" t="s" s="14">
         <v>12</v>
@@ -6611,28 +6629,28 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="6">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B191" s="7">
-        <v>45567.871504629734079648515192</v>
+        <v>45629.6273148149194063894792</v>
       </c>
       <c r="C191" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D191" s="9">
-        <v>45567.87187500010445001973452</v>
+        <v>45629.62754629640088787149128</v>
       </c>
       <c r="E191" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F191" s="11">
-        <v>45567</v>
+        <v>45629</v>
       </c>
       <c r="G191" s="12">
-        <v>1479500</v>
+        <v>1000</v>
       </c>
       <c r="H191" t="s" s="13">
-        <v>317</v>
+        <v>25</v>
       </c>
       <c r="I191" t="s" s="14">
         <v>12</v>
@@ -6640,28 +6658,28 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="6">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B192" s="7">
-        <v>45687.731446759363984019378188</v>
+        <v>45705.640381944549210255166716</v>
       </c>
       <c r="C192" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D192" s="9">
-        <v>45687.731747685289909945993892</v>
+        <v>45705.64103009269735840480054</v>
       </c>
       <c r="E192" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F192" s="11">
-        <v>45681</v>
+        <v>45705</v>
       </c>
       <c r="G192" s="12">
-        <v>12500</v>
+        <v>18000</v>
       </c>
       <c r="H192" t="s" s="13">
-        <v>103</v>
+        <v>317</v>
       </c>
       <c r="I192" t="s" s="14">
         <v>12</v>
@@ -6669,28 +6687,28 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="6">
+        <v>318</v>
+      </c>
+      <c r="B193" s="7">
+        <v>45677.66111111121581278815168</v>
+      </c>
+      <c r="C193" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D193" s="9">
+        <v>45677.661446759363960937069196</v>
+      </c>
+      <c r="E193" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F193" s="11">
+        <v>45677</v>
+      </c>
+      <c r="G193" s="12">
+        <v>4000</v>
+      </c>
+      <c r="H193" t="s" s="13">
         <v>319</v>
-      </c>
-      <c r="B193" s="7">
-        <v>45632.697905092697191205619796</v>
-      </c>
-      <c r="C193" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D193" s="9">
-        <v>45632.698506944549043058851204</v>
-      </c>
-      <c r="E193" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F193" s="11">
-        <v>45632</v>
-      </c>
-      <c r="G193" s="12">
-        <v>359500</v>
-      </c>
-      <c r="H193" t="s" s="13">
-        <v>320</v>
       </c>
       <c r="I193" t="s" s="14">
         <v>12</v>
@@ -6698,28 +6716,28 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="6">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B194" s="7">
-        <v>45601.397905092697119460210516</v>
+        <v>45673.74583333343802603583056</v>
       </c>
       <c r="C194" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D194" s="9">
-        <v>45601.398113426030452794021388</v>
+        <v>45673.746030092697285295540828</v>
       </c>
       <c r="E194" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F194" s="11">
-        <v>45601</v>
+        <v>45673</v>
       </c>
       <c r="G194" s="12">
         <v>13000</v>
       </c>
       <c r="H194" t="s" s="13">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I194" t="s" s="14">
         <v>12</v>
@@ -6727,28 +6745,28 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="6">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B195" s="7">
-        <v>45700.698368055660310038264756</v>
+        <v>45602.219710648252676899496932</v>
       </c>
       <c r="C195" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D195" s="9">
-        <v>45700.699502314919569300123948</v>
+        <v>45602.223738426030454686507124</v>
       </c>
       <c r="E195" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F195" s="11">
-        <v>45664</v>
+        <v>45602</v>
       </c>
       <c r="G195" s="12">
-        <v>6000</v>
+        <v>1000</v>
       </c>
       <c r="H195" t="s" s="13">
-        <v>323</v>
+        <v>25</v>
       </c>
       <c r="I195" t="s" s="14">
         <v>12</v>
@@ -6756,28 +6774,28 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="6">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B196" s="7">
-        <v>45707.672118055660326023394084</v>
+        <v>45567.871504629734079648515192</v>
       </c>
       <c r="C196" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D196" s="9">
-        <v>45707.672719907512177876625492</v>
+        <v>45567.87187500010445001973452</v>
       </c>
       <c r="E196" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F196" s="11">
-        <v>45707</v>
+        <v>45567</v>
       </c>
       <c r="G196" s="12">
-        <v>13000</v>
+        <v>1479500</v>
       </c>
       <c r="H196" t="s" s="13">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="I196" t="s" s="14">
         <v>12</v>
@@ -6785,28 +6803,28 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="6">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B197" s="7">
-        <v>45595.032789351956364129443132</v>
+        <v>45687.731446759363984019378188</v>
       </c>
       <c r="C197" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D197" s="9">
-        <v>45595.034270833437845614320444</v>
+        <v>45687.731747685289909945993892</v>
       </c>
       <c r="E197" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F197" s="11">
-        <v>45595</v>
+        <v>45681</v>
       </c>
       <c r="G197" s="12">
-        <v>1000</v>
+        <v>12500</v>
       </c>
       <c r="H197" t="s" s="13">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="I197" t="s" s="14">
         <v>12</v>
@@ -6814,28 +6832,28 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="6">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B198" s="7">
-        <v>45664.702476851956523825297576</v>
+        <v>45632.697905092697191205619796</v>
       </c>
       <c r="C198" t="s" s="8">
         <v>10</v>
       </c>
       <c r="D198" s="9">
-        <v>45664.702939814919486789321736</v>
+        <v>45632.698506944549043058851204</v>
       </c>
       <c r="E198" t="s" s="10">
         <v>10</v>
       </c>
       <c r="F198" s="11">
-        <v>45664</v>
+        <v>45632</v>
       </c>
       <c r="G198" s="12">
-        <v>2000</v>
+        <v>359500</v>
       </c>
       <c r="H198" t="s" s="13">
-        <v>46</v>
+        <v>326</v>
       </c>
       <c r="I198" t="s" s="14">
         <v>12</v>
@@ -6843,30 +6861,175 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="6">
+        <v>327</v>
+      </c>
+      <c r="B199" s="7">
+        <v>45601.397905092697119460210516</v>
+      </c>
+      <c r="C199" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D199" s="9">
+        <v>45601.398113426030452794021388</v>
+      </c>
+      <c r="E199" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F199" s="11">
+        <v>45601</v>
+      </c>
+      <c r="G199" s="12">
+        <v>13000</v>
+      </c>
+      <c r="H199" t="s" s="13">
+        <v>104</v>
+      </c>
+      <c r="I199" t="s" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s" s="6">
         <v>328</v>
       </c>
-      <c r="B199" s="7">
+      <c r="B200" s="7">
+        <v>45700.698368055660310038264756</v>
+      </c>
+      <c r="C200" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D200" s="9">
+        <v>45700.699502314919569300123948</v>
+      </c>
+      <c r="E200" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F200" s="11">
+        <v>45664</v>
+      </c>
+      <c r="G200" s="12">
+        <v>6000</v>
+      </c>
+      <c r="H200" t="s" s="13">
+        <v>329</v>
+      </c>
+      <c r="I200" t="s" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s" s="6">
+        <v>330</v>
+      </c>
+      <c r="B201" s="7">
+        <v>45707.672118055660326023394084</v>
+      </c>
+      <c r="C201" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D201" s="9">
+        <v>45707.672719907512177876625492</v>
+      </c>
+      <c r="E201" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F201" s="11">
+        <v>45707</v>
+      </c>
+      <c r="G201" s="12">
+        <v>13000</v>
+      </c>
+      <c r="H201" t="s" s="13">
+        <v>331</v>
+      </c>
+      <c r="I201" t="s" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s" s="6">
+        <v>332</v>
+      </c>
+      <c r="B202" s="7">
+        <v>45595.032789351956364129443132</v>
+      </c>
+      <c r="C202" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D202" s="9">
+        <v>45595.034270833437845614320444</v>
+      </c>
+      <c r="E202" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F202" s="11">
+        <v>45595</v>
+      </c>
+      <c r="G202" s="12">
+        <v>1000</v>
+      </c>
+      <c r="H202" t="s" s="13">
+        <v>25</v>
+      </c>
+      <c r="I202" t="s" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s" s="6">
+        <v>333</v>
+      </c>
+      <c r="B203" s="7">
+        <v>45664.702476851956523825297576</v>
+      </c>
+      <c r="C203" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D203" s="9">
+        <v>45664.702939814919486789321736</v>
+      </c>
+      <c r="E203" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F203" s="11">
+        <v>45664</v>
+      </c>
+      <c r="G203" s="12">
+        <v>2000</v>
+      </c>
+      <c r="H203" t="s" s="13">
+        <v>46</v>
+      </c>
+      <c r="I203" t="s" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s" s="6">
+        <v>334</v>
+      </c>
+      <c r="B204" s="7">
         <v>45593.655810185289694306484648</v>
       </c>
-      <c r="C199" t="s" s="8">
-        <v>10</v>
-      </c>
-      <c r="D199" s="9">
+      <c r="C204" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="D204" s="9">
         <v>45593.656990740845249864746256</v>
       </c>
-      <c r="E199" t="s" s="10">
-        <v>10</v>
-      </c>
-      <c r="F199" s="11">
+      <c r="E204" t="s" s="10">
+        <v>10</v>
+      </c>
+      <c r="F204" s="11">
         <v>45586</v>
       </c>
-      <c r="G199" s="12">
+      <c r="G204" s="12">
         <v>1000</v>
       </c>
-      <c r="H199" t="s" s="13">
+      <c r="H204" t="s" s="13">
         <v>25</v>
       </c>
-      <c r="I199" t="s" s="14">
+      <c r="I204" t="s" s="14">
         <v>12</v>
       </c>
     </row>
